--- a/data/ai_data.xlsx
+++ b/data/ai_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\text_mining_project -V2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58FA2651-48E2-4BCA-8F1F-BC701EDEAF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7EE040-679C-493E-A46A-1AACF20B1EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6F8EC6DD-DAE3-40A7-81C1-D9CCB48E07DD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="871">
   <si>
     <t>No</t>
   </si>
@@ -1788,21 +1788,904 @@
   <si>
     <t>https://api.semanticscholar.org/CorpusID: 245385821</t>
   </si>
+  <si>
+    <t>Introduction to artificial neural systems</t>
+  </si>
+  <si>
+    <t>Jacek M. Zurada received his MS and Ph.D. degrees (with distinction) in electrical engineering from the Technical University of Gdansk, Poland. Since 1989 he has been a Professor with the Electrical and Computer Engineering Department at the University of Louisville, Kentucky. He was Department Chair from 2004 to 2006. He has published over 350 journal and conference papers in the areas of neural networks, computational intelligence, data mining, image processing and VLSI circuits. INTRODUCTION TO ARTIFICIAL NEURAL SYSTEMS</t>
+  </si>
+  <si>
+    <t>Multiagent Systems: A Modern Approach to Dis- tributed Artificial Intelligence A Review</t>
+  </si>
+  <si>
+    <t>dent on automated intelligent systems; at the same time, these systems have become more and more complicated. Society’s expectation regarding the capabilities and intelligence of such systems has also grown. We have become a more complicated society with more complicated problems. As the expectation of intelligent systems rises, we discover many more applications for AI. Additionally, as the difficulty level and computational requirements of such problems rise, there is a need to distribute the problem solving. Although the field of multiagent systems and distributed AI is relatively young, the importance and applicability of this technology for solving today’s problems continues to grow. As the title indicates, Multiagent Systems: A Modern Approach to Distributed Artificial Intelligence covers the design and development of multiagent and distributed AI systems. The purpose of this book is to provide a comprehensive overview of the field. It is an excellent collection of closely related papers that provides a wonderful introduction to multiagent systems and distributed AI. The book provides not only basic introductory information but also detailed discussions covering the important topics in the field, practical examples and applications, and a section dedicated to the relationship between multiagent systems and various other research areas. This book compiles the important concepts and methodologies required to develop a multiagent system in an understandable, and comprehensive, manner. Not only does the book focus on the known solutions and issues, it also discusses the open questions and dilemmas. The prologue begins by defining distributed AI as “the study, construc-</t>
+  </si>
+  <si>
+    <t>6G White Paper on Edge Intelligence</t>
+  </si>
+  <si>
+    <t>In this white paper we provide a vision for 6G Edge Intelligence. Moving towards 5G and beyond the future 6G networks, intelligent solutions utilizing data-driven machine learning and artificial intelligence become crucial for several real-world applications including but not limited to, more efficient manufacturing, novel personal smart device environments and experiences, urban computing and autonomous traffic settings. We present edge computing along with other 6G enablers as a key component to establish the future 2030 intelligent Internet technologies as shown in this series of 6G White Papers. In this white paper, we focus in the domains of edge computing infrastructure and platforms, data and edge network management, software development for edge, and real-time and distributed training of ML/AI algorithms, along with security, privacy, pricing, and end-user aspects. We discuss the key enablers and challenges and identify the key research questions for the development of the Intelligent Edge services. As a main outcome of this white paper, we envision a transition from Internet of Things to Intelligent Internet of Intelligent Things and provide a roadmap for development of 6G Intelligent Edge.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence in Railway Infrastructure current research, challenges, and future opportunities</t>
+  </si>
+  <si>
+    <t>The railway industry has the potential to make a strong contribution to the achievementof various sustainable development goals,by an expansion of its role in the transportation system of different countries. To realize this, complex technological and societal challenges are to be addressed, along with the development of suitable state-of-the-art methodologies fully tailored to the particular needs of the wide variety of railway infrastructure types and conditions. Artificial intelligence (AI) methods have been increasingly and successfully applied to solve practical problems in the railway infrastructure domain for over two decades. This paper proposes a review of the development of AI methods in railway infrastructure. First, we present a survey limited to selected journal papers published between 2010 and 2022. Bibliographical statistics are obtained, showing the increasing number of contributions in this field. Then, we select key AI methodologies and discuss their applications in the railway infrastructure. Next, AI methods for key railway components are analyzed. Finally, current challenges and future opportunities are discussed.</t>
+  </si>
+  <si>
+    <t>Stock Market Forecasting Using Computational Intelligence: A Survey</t>
+  </si>
+  <si>
+    <t>Stock market plays a key role in economical and social organization of a country. Stock market forecasting is highly demanding and most challenging task for investors, professional analyst and researchers in the financial market due to highly noisy, nonparametric, volatile, complex, non-linear, dynamic and chaotic nature of stock price time series. Prediction of stock market is a crucial task and prominent research area in financial domain as investing in stock market involves higher risk. However with the development of computational intelligent methods it is possible to reduce most of the risk. In this survey paper, our focus is on application of computational intelligent approaches such as artificial neural network, fuzzy logic, genetic algorithms and other evolutionary techniques for stock market forecasting. This paper presents an up-to-date survey of existing literature on stock market forecasting based on computational intelligent methods. In this article, the selected papers are organized and discussed according to six main point of view: (1) the stock market analyzed and the related dataset, (2) the type of input variables investigated, (3) the pre-processing techniques used, (4) the feature selection techniques to choose effective variables, (5) the forecasting models to deal with the stock price forecasting problem and (6) performance metrics utilized to evaluate the models. The major contribution of this work is to provide the researcher and financial analyst a systematic approach for development of intelligent methodology to forecast stock market. This paper also presents the outlines of proposed work with the aim to enhance the performance of existing techniques.</t>
+  </si>
+  <si>
+    <t>AI 2013: Advances in Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>This book constitutes the refereed proceedings of the 26th Australasian Joint Conference on Artificial Intelligence, AI 2013, held in Dunedin, New Zealand, in December 2013. The 35 revised full papers and 19 revised short papers presented were carefully reviewed and selected from 120 submissions. The papers are organized in topical sections as agents; AI applications; cognitive modelling; computer vision; constraint satisfaction, search and optimisation; evolutionary computation; game playing; knowledge representation and reasoning; machine learning and data mining; natural language processing and information retrieval; planning and scheduling.</t>
+  </si>
+  <si>
+    <t>Ultraflexible and Mechanically Strong Double-Layered Aramid Nanofiber-Ti3C2Tx MXene/Silver Nanowire Nanocomposite Papers for High-Performance Electromagnetic Interference Shielding.</t>
+  </si>
+  <si>
+    <t>High-performance electromagnetic interference (EMI) shielding materials with ultraflexibility, outstanding mechanical properties and superior EMI shielding performances are highly desirable for modern integrated electronic and telecommunication systems in areas such as aerospace, military, artificial intelligence, smart and wearable electronics. Herein, ultraflexible and mechanically strong aramid nanofiber-Ti3C2Tx MXene/Ag nanowire (ANF-MXene/AgNW) nanocomposite papers with double-layered structures are fabricated via the facile two-step vacuum assisted filtration (TVAF) followed by hot-pressing approach. The resultant double-layered nanocomposite papers with a low MXene/AgNW content of 20 wt% exhibit excellent electrical conductivity of 922.0 S·cm-1, outstanding mechanical properties with tensile strength of 235.9 MPa and fracture strain of 24.8%, superior EMI shielding effectiveness (EMI SE) of 48.1 dB and high EMI SE/t of 10688.9 dB·cm-1, benefiting from the highly efficient double-layered structures, high-performance ANF substrate and extensive hydrogen bonding interactions. Particularly, the nanocomposite papers show the maximum electrical conductivity of 3725.6 S·cm-1 and EMI shielding effectiveness (EMI SE) of ~80 dB at the MXene/AgNW content of 80 wt% with an absorption-dominant shielding mechanism owing to the massive ohmic losses in highly conductive MXene/AgNW layer, multiple internal reflections between Ti3C2Tx MXene nanosheets and polarization relaxation of localized defects and abundant terminal groups. Compared with the homogeneously-blended ones, the double-layered nanocomposite papers possess greater advantages in electrical, mechanical and EMI shielding performances. Moreover, the multifunctional double-layered nanocomposite papers exhibit excellent thermal management performances such as high Joule heating temperature at low supplied voltages, rapid response time, sufficient heating stability and reliability. The results indicate that the double-layered nanocomposite papers have excellent potential for high-performance EMI shielding and thermal management applications in aerospace, military and artificial intelligence, smart and wearable electronics.</t>
+  </si>
+  <si>
+    <t>One Decade of Universal Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>The first decade of this century has seen the nascency of the first mathematical theory of general artificial intelligence. This theory of Universal Artificial Intelligence (UAI) has made significant contributions to many theoretical, philosophical, and practical AI questions. In a series of papers culminating in book (Hutter, 2005), an exciting sound and complete mathematical model for a super intelligent agent (AIXI) has been developed and rigorously analyzed. While nowadays most AI researchers avoid discussing intelligence, the awardwinning PhD thesis (Legg, 2008) provided the philosophical embedding and investigated the UAI-based universal measure of rational intelligence, which is formal, objective and non-anthropocentric. Recently, effective approximations of AIXI have been derived and experimentally investigated in JAIR paper (Veness et al. 2011). This practical breakthrough has resulted in some impressive applications, finally muting earlier critique that UAI is only a theory. For the first time, without providing any domain knowledge, the same agent is able to self-adapt to a diverse range of interactive environments. For instance, AIXI is able to learn from scratch to play TicTacToe, Pacman, Kuhn Poker, and other games by trial and error, without even providing the rules of the games. These achievements give new hope that the grand goal of Artificial General Intelligence is not elusive. This article provides an informal overview of UAI in context. It attempts to gently introduce a very theoretical, formal, and mathematical subject, and discusses philosophical and technical ingredients, traits of intelligence, some social questions, and the past and future of UAI.</t>
+  </si>
+  <si>
+    <t>150314 State of the Art of Artificial Intelligence and Predictive Analytics in the E &amp; P Industry :</t>
+  </si>
+  <si>
+    <t>Artificial intelligence (AI) has been used for more than two decades as a development tool for solutions in several areas of the E&amp;P industry: virtual sensing, production control and optimization, forecasting, and simulation, among many others. Nevertheless, AI applications have not been consolidated as standard solutions in the industry, and most common applications of AI still are case studies and pilot projects. In this work, an analysis of a survey conducted on a broad group of professionals related to several E&amp;P operations and service companies is presented. This survey captures the level of AI knowledge in the industry, the most common application areas, and the expectations of the users from AI-based solutions. It also includes a literature review of technical papers related to AI applications and trends in the market and R&amp;D. The survey helped to verify that (a) data mining and neural networks are by far the most popular AI technologies used in the industry; (b) approximately 50% of respondents declared they were somehow engaged in applying workflow automation, automatic process control, rule-based case reasoning, data mining, proxy models, and virtual environments; (c) production is the area most impacted by the applications of AI technologies; (d) the perceived level of available literature and public knowledge of AI technologies is generally low; and (e) although availability of information is generally low, it is not perceived equally among different roles. This work aims to be a guide for personnel responsible for production and asset management on how AI-based applications can add more value and improve their decision making. The results of the survey offer a guideline on which tools to consider for each particular oil and gas challenge. It also illustrates how AI techniques will play an important role in future developments of IT solutions in the E&amp;P industry. Introduction While there is hardly a rigorous definition of the term artificial intelligence (AI) that is unequivocally accepted, the tools of AI and its intended uses have been well studied for decades and many applications have appeared. Loosely speaking, AI is the capability of machines (usually in the form of computer hardware and software) to mimic or exceed human intelligence in everyday engineering and scientific tasks associated with perceiving, reasoning, and acting. Since human intelligence is multifaceted, so is AI, comprising goals that range from knowledge representation and reasoning, to learning, to visual perception and language understanding (Winston 1992). AI techniques have been present in the E&amp;P industry for many years. A quick literature search reveals application of AI in SPE scientific and engineering papers as early as in the 1970s. There are numerous references about the applications of neural networks, fuzzy logic, genetic algorithms, expert systems, and other artificial techniques in the resolution of problems in diverse areas, such as reservoir simulation, production optimization, process control, and fault detection and diagnosis, among many others. AI is an area of great interest in the E&amp;P industry, mainly in applications related to production control and optimization, proxy model simulation, and virtual sensing. The most popular techniques are artificial neural networks, fuzzy logic, and genetic algorithms, with interesting developments in hybrid and nontraditional techniques. There has been recent increase in such AI-based commercial applications for production management. While the full impact of such applications is still being realized, there are already solutions in the market with a positive impact in the E&amp;P industry.</t>
+  </si>
+  <si>
+    <t>Editorial for the Special Section on Humans, Algorithms, and Augmented Intelligence: The Future of Work, Organizations, and Society</t>
+  </si>
+  <si>
+    <t>Recent developments in artificial intelligence (AI) have increased interest in combining AI with human intelligence to develop superior systems that augment human and artificial intelligence. In this paper, augmented intelligence informally means computers and humans working together, by design, to enhance one another, such that the intelligence of the resulting system improves. Intelligence augmentation (IA) can pool the joint intelligence of humans and computers to transform individual work, organizations, and society. Notably, applications of IA are beginning to emerge in several domains, such as cybersecurity, privacy, counterterrorism, and healthcare, among others. We provide a brief summary of papers in this special section that represent early attempts to address some of the rapidly emerging research issues. We also present a framework to guide research on IA and advocate for the important implications of IA for the future of work, organizations, and society. We conclude by outlining promising research directions based on this framework for the information systems and related disciplines.</t>
+  </si>
+  <si>
+    <t>How do we move towards true artificial intelligence</t>
+  </si>
+  <si>
+    <t>At present, the development of artificial intelligence technology has entered a new bottleneck period, and the algorithm dividend based on statistics has been exhausted. In the future, we should pay more attention to improving the efficient, intelligent collaboration among humans, machines, and the environment. This review first discusses the bottleneck problems encountered in the current artificial intelligence technology, then analyzes the essence of human intelligence and the differences, advantages, and disadvantages of the current machine intelligence and human intelligence. Based on this, it puts forward that the enhancement point of artificial intelligence technology is to enhance the efficient cooperation of the human-computer environment and states our solution, namely the deep situation awareness method based on human-computer integration technology. In the end, we put forward some thoughts about intelligence.</t>
+  </si>
+  <si>
+    <t>Patient Attitude on the Application of Artificial Intelligence in Diabetes Care</t>
+  </si>
+  <si>
+    <t>The integration of artificial intelligence (AI) into diabetes care holds the potential to transform patient management and improve outcomes, especially in Malaysia, where diabetes represents a major public health challenge. However, the adoption and effectiveness of AI in healthcare are significantly impacted by patient attitudes. This paper addresses the gap in understanding these attitudes. The primary goal of this study is to investigate the perspectives of diabetic patients on the use of AI applications and tools in diabetes care. This study also examined the patterns of acceptance and understanding of AI among diabetic patients. This study used qualitative methods using in-depth interviews with seventeen Malaysian diabetic patients in Hospital Tengku Ampuan Rahimah Klang (HTAR), Malaysia. The interview lasted two weeks, from August 8, 2023, to August 22, 2023. All interviews were audio-recorded and transcribed word-for-word. The transcribed content was then organized and coded using ATLAS.ti version 8. Thematic analysis was performed in accordance with established guidelines for data analysis. Three key themes emerged from participant interviews regarding the patients' attitudes toward AI application in diabetes care. These themes were perceived acceptability, perceived benefits of using AI tools, and perceived need. The majority of participants expressed their positive view of using AI tools. The findings of this study lay the groundwork for a theoretical framework aimed at understanding patients' stances on AI applications in diabetic care, emphasizing the health, technological, and social experiences that influence their perspectives on AI in this context.</t>
+  </si>
+  <si>
+    <t>Construction of Enterprise Business Management Analysis Framework in the Development of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>In this era of rapid development, artificial intelligence has gradually entered our life, as a will be applied to the global technology, artificial intelligence in many fields have broad application prospects, artificial intelligence as the product of social development and technological innovation, has become a new round of scientific and technological innovation and the core driving force, is on the world economy, social progress and people’s life has had an extremely profound impact. The commercial application of artificial intelligence will change the internal operation and production and operation process of enterprises, and brings many challenges and reform opportunities for enterprise management. Article for the impact of artificial intelligence on the enterprise business management, analyze the application of enterprise business management and the impact of the technology application to the enterprise, and combined with some possible problems, in order to make artificial intelligence technology can be better applied in the enterprise management, put forward part of the corresponding solutions.</t>
+  </si>
+  <si>
+    <t>Application and existing problems of computer network technology in the field of artificial intelligence</t>
+  </si>
+  <si>
+    <t>With the development of science and technology, computer technology is more and more widely used in people's life. As a branch of computer technology, artificial intelligence technology is also gradually developing and expanding, affecting people's life. Nowadays, the processing ability shown by simple computer technology has gradually lagged behind the times. If you want more convenient data processing, artificial intelligence is an excellent solution. Agent technology in artificial intelligence makes artificial intelligence have stronger data processing ability and learning ability than computer technology, and can make decisions quickly according to data information. Artificial intelligence technology can promote automation and intelligence in various industries and improve the production efficiency of enterprises. Starting from the elaboration of artificial intelligence, this paper deeply explores the relationship between artificial intelligence and computer, analyzes the development status of artificial intelligence and computer, and puts forward the technical problems between artificial intelligence and computer, so as to provide reference for the further development of artificial intelligence.</t>
+  </si>
+  <si>
+    <t>The Risks and Countermeasures of Accounting Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>A Review on Artificial Intelligence with Deep Human Reasoning</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence (AI) is a broad term that can be construed to mean a focusing computer programming and development that is designed to train machines and to perform task. Artificial intelligence can be used to test theories of reasoning like cognitive reasoning and consciousness. Research has been conducted on the development of machines with human behavior and cognitive characteristics that are related to consciousness. Artificial Intelligence and Reasoning that are dealt with, can necessarily solve problems related to mental health issues that humans find complex, but research on new interaction techniques and human for cooperation theories, technologies limited the issues and challenges facing the application of artificial reasoning. Here in this paper, the relation between artificial intelligence human reasoning that is also called as AI reasoning or artificial reasoning has been studied. Artificial intelligence impacts reasoning and how artificial reasoning can be used in day-to-day activities to regain our mental health. Moreover, this work focuses on problems that can be solved with AI Reasoning in trying to find the possible solutions.</t>
+  </si>
+  <si>
+    <t>Research on the Application of Artificial Intelligence in Hotels</t>
+  </si>
+  <si>
+    <t>At present, driven by new theories and technologies such as the Internet and big data, artificial intelligence is developing rapidly, and all walks of life are actively integrating with artificial intelligence technology to advance the development of the industry. This article takes the application of artificial intelligence in hotels as the research object, preliminaries analyzes the current status and existing problems of artificial intelligence development in the hotel industry, and proposes relevant solution strategies, hoping to provide certain ideas for the efficient application of artificial intelligence in hotels. To help hotel companies use artificial intelligence more rationally to enhance guest loyalty and satisfaction.</t>
+  </si>
+  <si>
+    <t>Analysis on the application of artificial intelligence in marketing</t>
+  </si>
+  <si>
+    <t>With the continuous development of modern information technology, various new development technologies are gradually emerging. As an important development content of the discipline of computer science, artificial intelligence can simulate human activities through intelligent systems or intelligent machines, so as to extend people’s intelligence. Artificial intelligence has been widely used in all walks of life, combining artificial intelligence and marketing technology, can effectively innovate the traditional marketing methods, improve the overall development quality of marketing, through the analysis of artificial intelligence in the field of marketing application status, clear the advantages of artificial intelligence in the field of marketing, so as to better promote the overall quality of artificial intelligence in marketing development.</t>
+  </si>
+  <si>
+    <t>Application of artificial intelligence in computer network technology</t>
+  </si>
+  <si>
+    <t>With the development of science and technology, artificial intelligence has been widely used in many fields, smart TVs, intelligent sweeping robots, intelligent voice, etc. are quiet trigger great changes in human society. At the same time, people are also exploring the integration and development of computer network technology and artificial intelligence, in order to use artificial intelligence advantages improve the accuracy and efficiency of data processing. The author first analyzes the concept of artificial intelligence, and then analyzes artificial intelligence in computer network technology in detail. The application of artificial intelligence in the field of computer is finally discussed.</t>
+  </si>
+  <si>
+    <t>Applications, Risks and Countermeasures of Artificial Intelligence in Education</t>
+  </si>
+  <si>
+    <t>The application of artificial intelligence in education has greatly affected school management, teachers' teaching and students' learning, and has an important influence on the mechanism and mechanism of learning process. The concept of artificial intelligence is to simulate human intelligence by machine, thus completing specific roles and tasks, and has the characteristics of convenience, intelligence and interaction. It is mainly applied to computer vision, natural language processing, biometric recognition, speech recognition, human-computer interaction and other technologies in the field of education, which brings space for the development of architecture, medicine and chemistry. However, AI also brings about the risk of decisionmaking mistakes, career substitution, privacy leakage, information cocoon house and data bias. In order to avoid these risks effectively, this paper puts forward solutions from five perspectives: the state, product developers, educational managers, teachers and students, so as to correctly understand the relationship between artificial intelligence and education, explore the application mode of artificial intelligence in the field of education, and ensure the deep integration of artificial intelligence and education.</t>
+  </si>
+  <si>
+    <t>The Role of Artificial Intelligence (AI) in Transforming Biomedical Imaging: A Comprehensive Overview</t>
+  </si>
+  <si>
+    <t>The integration of Artificial Intelligence (AI) in biomedical imaging heralds a transformative era in medical diagnostics and research. This comprehensive overview explores the multifaceted impact of AI on various imaging modalities, emphasizing its potential to revolutionize disease detection, characterization, and treatment planning. AI applications, particularly machine learning and deep learning, enhance the analysis of intricate imaging data, providing quicker and more accurate insights. This review delves into AI's role in automating diagnosis through the development of sophisticated algorithms, enabling faster and more precise identification of diseases across diverse medical imaging platforms. Furthermore, AI contributes to improving image quality, facilitating early detection of abnormalities, and enhancing decision support systems for clinicians. Beyond diagnosis, AI facilitates personalized medicine by tailoring treatment strategies based on individual patient data extracted from imaging. The ethical considerations and privacy implications of handling sensitive medical information are also discussed, ensuring a balanced perspective on the adoption of AI in healthcare. As AI continues to advance, this overview concludes with insights into future trends, challenges, and the collaborative synergy between technology, healthcare practitioners, and researchers, underscoring the ongoing evolution of biomedical imaging through artificial intelligence.</t>
+  </si>
+  <si>
+    <t>Analysis of the Impact of Artificial Intelligence on Electricity Consumption</t>
+  </si>
+  <si>
+    <t>The in-depth development and widespread application of artificial intelligence technology will have significant impact on electricity demand. However, there are few comprehensive analyses. This article will analyze the direct and indirect impact respectively. For direct impact, artificial intelligence requires various data centers to provide huge computing and storage capabilities, which will increase the electricity demand of data centers; for indirect impact, artificial intelligence will also optimize the time and space distribution of electricity demand and deepen energy conservation and power saving in the whole society. Research shows that the development of artificial intelligence will increase the electricity consumption of data centers, and it is necessary to plan ahead for the infrastructure related to the electricity consumption of artificial intelligence; artificial intelligence plays an important role in promoting the development of demand response, and a largescale joint dispatch mechanism of electricity and computing power for the power market should be explored; data centers have a large space for energy conservation and carbon reduction, and a sound electricity price mechanism that comprehensively considers green electricity consumption and energy efficiency should be established to promote data centers to widely participate in green electricity transactions and actively reduce their own PUE.</t>
+  </si>
+  <si>
+    <t>Exploration and Reflection of Legal Artificial Intelligence in Japan</t>
+  </si>
+  <si>
+    <t>It has been more than 60 years since the concept of artificial intelligence was established in 1956. In recent years, with the innovation and development of technology, especially the emergence of ChatGPT, it is expected that generative artificial intelligence models will lead to new breakthroughs in various industries. This thesis focuses on Japan, which is adjacent to China and belongs to the same continental legal system, and reviews the attempt of the fifth-generation computing institution construction legal expert system after combining symbolism and artificial intelligence in the 1990s in Japan, and analyzes the relevant research conducted by Japan in the field of artificial intelligence jurisprudence after that, as well as the new trends that have emerged in the field of legal artificial intelligence research after the advent of ChatGPT. This thesis will finally compare the research situation of the two countries in the field of artificial intelligence jurisprudence and comprehensively analyze the experience of Japan in the research, putting forward views on how to make China's legal artificial intelligence research smoother based on the lessons learned from past failures.</t>
+  </si>
+  <si>
+    <t>Research on Artificial Intelligence Algorithm and Its Application in Games</t>
+  </si>
+  <si>
+    <t>With the in-depth development of intelligent technology, game artificial intelligence (AI) has become the technical core of improving the playability of a game and the main selling point of game promotion, deepening the game experience realm. Modern computer games achieve the realism of games by integrating graphics, physics and artificial intelligence. It is difficult to define the meaning of realistic game experience, but generally speaking, it usually refers to the immersion of the game and the intelligence of non-player characters in the game. As the technical core of improving game playability and the selling point of many commercial games, game artificial intelligence gives players a way to interact with non-player characters in the game, and promotes the realm of game experience to a higher level. Based on this, this paper analyzes the history and present situation of artificial intelligence in game development, and puts forward the possible changes and impacts of artificial intelligence technology based on machine learning on game development in the future.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence Surpassing Human Intelligence: Factual or Hoax</t>
+  </si>
+  <si>
+    <t>Artificial intelligence is one of the most trending topics in the field of Computer Science which aims to make machines and computers ‘smart’. There are multiple diverse technical and specialized research associated with it. Due to the accelerating rate of technological changes, artificial intelligence has taken over a lot of human jobs and is giving excellent results that are more efficient and effective, than humans. However, a lot of time there has been a concern about the following: will artificial intelligence surpass human intelligence in the near future? Are computers' ever accelerating abilities to outpace human jobs and skills a matter of concern? The different views and myths on the subject have made it even a more than just a topic of discussion. In this research paper, we will study the existing facts and literature to understand the true definitions of artificial intelligence (AI) and human intelligence (HI) by classifying each of its types separately and analyzing the extent of their full capabilities. Later, we will discuss the possibilities if AI eventually can replace human jobs in the market. Finally, we will synthesize and summarize results and findings of why artificial intelligence cannot surpass human intelligence completely in the future.</t>
+  </si>
+  <si>
+    <t>Decoding Justice: The Synergy of Artificial Intelligence and Machine Learning in the Legal Landscape</t>
+  </si>
+  <si>
+    <t>The rapid integration of Artificial Intelligence (AI), Machine Learning (ML), and Internet of Things (IoT) technologies holds significant promise for enhancing human-centric applications, particularly in the domain of law enforcement. This paper explores the application of AI and ML in crime prevention and resource allocation, pivotal areas of concern for law enforcement agencies (LEAs) globally. By utilizing historical crime data, sensory inputs, and advanced analytics, this study contributes to the evolving discourse on smart policing and proactive crime strategies. Our objective is to facilitate the transformation of LEAs from primarily reactive entities into proactive crime preventers through the adoption of predictive analytics, facial recognition enhanced surveillance, and natural language processing for efficient data analysis. We emphasize that collaborative efforts with AI experts ensure the responsible use of technology, meticulously balancing security imperatives with privacy concerns.</t>
+  </si>
+  <si>
+    <t>Application of artificial intelligence in computer network technology in the era of big data</t>
+  </si>
+  <si>
+    <t>Today, with the progress of computer network technology, the advantages of artificial intelligence gradually began to show and become a new product under the development of the current era. At present, the strength of artificial intelligence technology lies in its data analysis and processing ability, because with the continuous development and progress of the society, the difficulty of processing data and information is becoming more and more complex for many years, and the processing ability of computers has begun to show shortcomings. The use of artificial intelligence can solve this problem well, and it can also put forward solutions according to the corresponding data problems, to timely deal with all kinds of data information. This paper mainly analyzes the application of artificial intelligence in computer network in the era of big data, and discusses the application and significance of artificial intelligence in big data.</t>
+  </si>
+  <si>
+    <t>Study on the Application Fields and Development Prospects of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Since the world entered the Internet age, various industries have developed rapidly, as has the industry of artificial intelligence. Moreover, there is a wide range of application areas in artificial intelligence, including industry, computer, education, and intelligent robots. With the rapid development of science and technology, it is believed that the artificial intelligence may develop towards the "artificial intelligence +" era and strong artificial intelligence, which will be comprehensively analyzed in terms of definition, development, and application areas. Especially the analysis of intellectual property rights is of reference significance to the intellectual property planning of domestic enterprises.</t>
+  </si>
+  <si>
+    <t>Artificial intelligence and modern sports education technology</t>
+  </si>
+  <si>
+    <t>Artificial intelligence is a comprehensive cutting-edge discipline which is developing, and an important research direction in the fields of science computer and technology. This paper uses the principles and methods of artificial intelligence on the basis of describing the concept and research areas of artificial intelligence, focuses on in-depth analysis and discussion of applicable perspective and development of artificial intelligence in modern physical education technology, and raises the corresponding development strategies to the use of artificial intelligence in modem sports educational technology, in order to provide the theoretical support for the establishment and development of modern physical education technical disciplines.</t>
+  </si>
+  <si>
+    <t>The Influence and Application of Artificial Intelligence on the Political Development of New Media in China</t>
+  </si>
+  <si>
+    <t>At present, in the field of artificial intelligence, China and the United States are not only engaged in technological competition, but also in a political war. China’s ideology makes Chinese people accustomed to giving up part of the right of privacy in order to get better public services, and artificial intelligence just needs a huge database. Therefore, the government can use artificial intelligence recommendation technology in the field of new media to guide citizens’ political views, obtain effective data while strengthening national control, promote the development of artificial intelligence technology, and enhance the importance of China’s ideology to a certain extent, so that China can maintain a relatively leading position in the current competition. Based on this, this paper analyzes the influence and application of artificial intelligence on the development of new media politics in China.</t>
+  </si>
+  <si>
+    <t>Research and Application of Artificial Intelligence and Big Data in Infectious Disease Prevention and Control</t>
+  </si>
+  <si>
+    <t>With the continuous spread and globalization of infectious diseases, infectious disease prevention and control has become an important task for both countries and the world. Traditional infectious disease monitoring methods often rely on manual collection and analysis of data, which is inefficient and easily limited by human errors. However, the development of artificial intelligence and big data technology has provided new opportunities for infectious disease prevention and control. This article introduces the application of artificial intelligence in infectious disease monitoring. By using artificial intelligence algorithms and models, real-time monitoring and analysis of infectious disease data can be carried out, predicting the spread trend and risk of infectious diseases. This helps to detect and report infectious disease outbreaks, thus taking corresponding prevention and control measures and reducing the spread and impact of the epidemic. At the same time, this article explores the application of big data in infectious disease prevention and control. By using big data technology, in-depth mining and analysis of patient case data, virus gene sequences, transmission chain information, and other data can be carried out to discover the characteristics and patterns of infectious diseases, and be used to build an infectious disease warning system to predict and prevent the occurrence of infectious diseases in advance. Finally, this article discusses the application cases of artificial intelligence and big data in infectious disease prevention and control. By combining artificial intelligence and big data technology, the entire process of monitoring and management of infectious diseases can be achieved.</t>
+  </si>
+  <si>
+    <t>Engagement of Artificial Intelligence in Higher Education: University of Petra as a Case Study</t>
+  </si>
+  <si>
+    <t>A survey of 105 instructors from University of Petra (UOP) Faculties of Arts and Science (FAS) and Information Technology (FIT) was conducted, expressing their views on the efficiency of the current artificial intelligence (AI) tools against human cognitive abilities. The survey examined what instructors expect from the development of AI, who will adopt AI technologies, whether economies will accelerate adoption of AI technologies in the education sector, how widespread adoption of these technologies will impact different countries, and what risks AI might present to individual privacy. This survey is intended to find out what UOP instructors expect AI to become in education and how they expect to incorporate it. This will help to yield useful insights to guide strategies to facilitate effective implementation of AI within this context. In addition, the results will help UOP prepare for AI's chanaing landscape and what it means for higher education.</t>
+  </si>
+  <si>
+    <t>Application of Artificial Intelligence and Virtual Reality Technology in the Construction of University Physical Education</t>
+  </si>
+  <si>
+    <t>The progress of artificial intelligence and virtual reality technology has provided convenience to all sectors of the society. With the support of the core algorithm of artificial intelligence, technicians can develop, design and optimize artificial intelligence systems so that they can have intelligence similar to the human brain and simulate human intelligent behavior. Artificial intelligence can perform model independent data processing through feature learning, or use feature engineering for human data processing. Virtual reality technology uses a computer to generate a simulation environment, which is an interactive three-dimensional dynamic visual scene and entity behavior system simulation that integrates multiple information, immersing users in it. Based on this, the paper conducts research and discussion from the following aspects: firstly, the relevant concepts of artificial intelligence and virtual reality are reviewed; secondly, the application points of artificial intelligence and virtual reality in universities are discussed, including the application of various technologies, the content and the equipment selection in the application of artificial intelligence and virtual reality.</t>
+  </si>
+  <si>
+    <t>Risks and Countermeasures of Artificial Intelligence for College Students' Growth</t>
+  </si>
+  <si>
+    <t>With the development of the times, artificial intelligence is also rapidly updating, bringing great convenience to people's lives, but also bringing many risks and challenges to college students. Currently, under the impact of artificial intelligence, college students are facing risks such as weakening their dominant position, obliterating value consensus, and reducing innovative thinking during their growth. The main reasons for these risks are insufficient teacher guidance, technical limitations, and insufficient government investment. In the future, we can explore Countermeasures based on the three major factors in education: educators, educational objects, and educational intermediaries, in order to better build an intelligent education ecosystem and cultivate creative talents required for the new era.</t>
+  </si>
+  <si>
+    <t>Analysis of Systematic Reform of Future Teaching in the Age of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Artificial intelligence has developed rapidly in recent years, which not only brings convenience to people’s lives, but also plays an important role in education. In the past, teachers mainly relied on relevant teaching materials to prepare lessons, but now teachers can use artificial intelligence technology to prepare lessons, which reduces the burden of preparing lessons for teachers. Artificial intelligence, referred to as AI for short, is a branch of computer science, and it is a discipline that studies how to make computers simulate people’s thinking and intelligent behavior. The application of artificial intelligence in education can promote education equality and improve teaching efficiency. For example, in some remote mountain schools, educational resources are scarce. The application of artificial intelligence can integrate and share educational resources to the network platform to achieve education equality. Then, this paper analyzes and explores how to change the teaching methods in the future. Starting from the current situation of the development of artificial intelligence in China and combining with the current teaching, it continuously analyzes and studies the teaching methods incorporating artificial intelligence to promote the systematic reform and development of future teaching.</t>
+  </si>
+  <si>
+    <t>Opportunities and Challenges Artificial Intelligence in Pharmacology : Artificial Intelligence in Pharmacology</t>
+  </si>
+  <si>
+    <t>This study explores the advancements in artificial intelligence (AI) and machine learning (ML) applications in pharmacology, emphasizing their role in enhancing drug discovery, development, and personalized treatment plans. The most significant achievement of this research is the demonstration of how AI techniques, particularly deep learning models, can effectively analyze complex biological data to predict drug interactions and optimize therapeutic outcomes. By integrating AI with traditional pharmacological methods, this study highlights the potential for reducing clinical trial failures and improving patient outcomes. Additionally, the research underscores the necessity for regulatory initiatives to promote data sharing, facilitating the development of robust AI models in pharmacology. Overall, this work contributes valuable insights into the transformative impact of AI on the future of drug development and clinical practice.</t>
+  </si>
+  <si>
+    <t>P3128/D01, Aug 2024 - IEEE Draft Recommended Practice for The Evaluation of Artificial Intelligence (AI) Dialogue System Capabilities</t>
+  </si>
+  <si>
+    <t>An evaluation framework for the intelligence capabilities of artificial intelligence (AI) dialogue systems such as chatbots, consulting terminals, or operation interfaces is established in this recommended practice. The recommended practice classifies the intelligence capabilities of an AI dialogue system into three categories—cognitive intelligence, emotional intelligence, and system completeness. For each class, the capabilities are subdivided into five intelligence levels, from the lowest level L1 to the highest level L5, with the performance criteria clarified at each level by an evaluation checklist.</t>
+  </si>
+  <si>
+    <t>Benefits of Artificial Intelligence in Medicine</t>
+  </si>
+  <si>
+    <t>Artificial intelligence is one of the most discussed topics of the present time. The burning question of today about artificial intelligence is “will it be beneficial or dangerous for a human being”. This research paper analyzes the benefits of artificial intelligence in medicine. It examines how artificial intelligence assists the medical field as well as how patient's health is affected using this popular phenomenon in diagnosing diseases, patient's treatment, reducing errors, and virtually being present with the patients. Finally, the paper reveals how artificial intelligence may have an impact on medical science. A survey was conducted to learn about people's perspective towards artificial intelligence in medicine and the results are shared in the paper.</t>
+  </si>
+  <si>
+    <t>A Study of College English Translation Teaching in the Age of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>At present, artificial intelligence technology has made a major breakthrough. Big data, cloud computing, language recognition, deep learning and other artificial intelligence technologies are widely used in the field of education and teaching, which not only changes students' traditional learning methods, but also promotes the innovation of teachers' teaching methods and teaching functions. The application of artificial intelligence technology, especially language translation technology in language teaching, has brought new opportunities and challenges for the development of language teaching in colleges. In this paper, artificial intelligence and its development are briefly introduced; then the influence of artificial intelligence on college English translation teaching are analysed; finally, college English translation teaching under the background of artificial intelligence is expounded.</t>
+  </si>
+  <si>
+    <t>Impact of Emotional Intelligence and Artificial Intelligence on Employee Retention: A Review of the Service Industry</t>
+  </si>
+  <si>
+    <t>Employee retention is one of the biggest challenges in today’s work environment. Organizations are constantly working on different tactics and strategies at organizational and individual levels to retain their talent. To handle the scenario, Artificial intelligence (AI) and Emotional Intelligence (EI) are emerging as significant dimensions to be taken up for the research. Thus, this study aims to examine the role of emotional and artificial intelligence in retaining employees. To investigate the association between these two important variables, a review of the literature was conducted. The findings demonstrate that much research has validated the association between AI and EI and the impact thereof on employee retention.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence of Platforms Talent Management Diversity, Equality, and Inclusion Employee Satisfaction</t>
+  </si>
+  <si>
+    <t>The research highlights the growing prevalence of artificial intelligence (AI) DEI made up the respondents that were chosen for the study. In order to help enterprises embrace AI effectively and meet DEI aims, this research study proposes a decision model. The research has been carried out within the framework of Indian corporations. The author has put out a model that provides a thorough framework to direct decision-making processes by outlining important factors, moral precepts, and implementation techniques. Organizations may maximize AI's potential while reducing bias, advancing justice, and fostering inclusivity in the workplace by fusing AI technology with DEI programs. Artificial Intelligence (AI)'s role in achieving the DEI (diversity, equality, and inclusion) goals .It is commonly acknowledged that creating and overseeing diverse teams has many advantages, including fostering innovation and creativity, improving decision-making, raising employee productivity, and improving retention. Businesses that employ a diverse workforce have an edge over rivals. Despite the clear advantages of having a diverse workforce, research indicates that businesses have not succeeded in implementing diversity initiatives. According to research, using AI in talent acquisition is becoming more and more crucial for creating a diverse workforce. DEI can be measured in a number of ways, such as by monitoring demographic information, examining employee happiness and engagement, and applying particular metrics to evaluate the advancement of racial equity and inclusion. Fair evaluation based on objective data, real-time feedback, support for personalized goal setting, adaptability to changing job requirements, ethical considerations, and privacy protection are the essential components of AI-based employee performance evaluation.</t>
+  </si>
+  <si>
+    <t>Promoting Digital Campus to Smart Campus Based on Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>In this paper, combined with the problems existing in the current campus and based on the advanced technology of artificial intelligence, we propose a five-tier framework model for building a smart campus, and describe the specific application practice of the framework in detail.</t>
+  </si>
+  <si>
+    <t>Informatization of Constructive English Learning Platform Based on Artificial Intelligence Algorithm</t>
+  </si>
+  <si>
+    <t>In recent years, intelligence is the new direction of today's social development, and it is also a new feature of the development of informatization. With the rapid development of technologies such as artificial intelligence, the Internet of Things, big data and cloud computing, smart products and devices such as smart homes, smart robots, smart toys, and smart buildings have emerged, which have brought great changes to people's life and work styles. Through the constructive research on artificial intelligence algorithms, this paper designs a relevant information-based English learning platform, which can greatly improve the efficiency of English learning in the traditional textbook mode, and cultivate the interest and enthusiasm of college students to learn English. Through the research of artificial intelligence algorithm, this paper finds that informatization of constructive English learning platform focuses on building the ecological environment of students' autonomous learning, which can greatly improve students' autonomous learning ability, it take the student as the center, to provide learning resources and learning methods, at the time let the students actively constructing autonomous learning awareness, respect and encourage students to have different progress and development. The final results of the study show that the number of students who choose learning interaction is the largest, accounting for 41%, followed by the number of students who choose independent learning, accounting for 31%. It can be concluded that students attach most importance to learning interaction, which can greatly improve students' enthusiasm and initiative in learning.</t>
+  </si>
+  <si>
+    <t>Research and application of artificial intelligence in law</t>
+  </si>
+  <si>
+    <t>With the development of science and technology, artificial intelligence is more and more widely used, and artificial intelligence technology can be seen everywhere in people’s life. The combination of artificial intelligence and law has become a hot topic in recent years. Artificial intelligence technology can provide judges with objective, factual and statistical data to help judges better hear cases. Based on a large number of factual civil judgment theories, the computer can extract the features, construct the knowledge map, and realize the in-depth learning of the artificial neural network. The fitting of the artificial neural network to various discretionary factors can meet the needs of the complexity of discretionary factors. Moreover, the artificial neural network can select the implicit maturity and the number of neurons in the discretion factors, realize knowledge transformation by defining matching rules, and learn big data on the basis of classification rules. These advantages of artificial intelligence can help judge cases. As long as artificial intelligence technology can be applied properly, our legal system can be improved.</t>
+  </si>
+  <si>
+    <t>Personalized Product Packaging Design System Driven by Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>With the development of artificial intelligence technology, product packaging design increasingly depends on intelligence. Personalized packaging is different in product design. This method is to analyze the factors such as different consumer groups, consumption needs and purchasing habits, and then carry out product packaging design. In order to make the product packaging attractive enough, this paper uses artificial intelligence to drive the system construction of packaging design. This paper mainly uses the experimental method and investigation method to explore the product packaging design system and its personalized packaging method. The experimental results show that the running time of the packaging system designed in this paper is kept within 1s, which can meet the basic requirements. Based on artificial intelligence technology, using data mining, image processing and other related algorithms, a personalized product packaging design system is developed. The system can automatically generate the corresponding packaging design scheme according to different customer needs and brand characteristics, and provide a variety of options and free modification functions.</t>
+  </si>
+  <si>
+    <t>Research on the Application of Artificial Intelligence Technology in Microelectronics Testing and Fault Diagnosis</t>
+  </si>
+  <si>
+    <t>This paper explores the integration of Artificial Intelligence (AI) technologies in the field of microelectronics testing and troubleshooting. Traditional methods for testing and troubleshooting microelectronic devices often face challenges such as high complexity, time-consumption, and the need for expert intervention. AI technologies, with their advanced capabilities in machine learning, neural networks, and expert systems, offer promising solutions to these problems. This study provides an overview of the key AI approaches employed in microelectronics, discusses their implementation in various test and diagnostic scenarios, and evaluates their impact in terms of improved accuracy, efficiency, and automation. Through a detailed analysis of case studies and real-world applications, the paper demonstrates how AI-driven approaches are revolutionizing the microelectronics industry, paving the way for more reliable and sophisticated electronic devices. The study concludes with a discussion of the current limitations of AI technologies in the field and suggests potential directions for future research and development.</t>
+  </si>
+  <si>
+    <t>Brain inspired cognitive artificial intelligence for knowledge extraction and intelligent instrumentation system</t>
+  </si>
+  <si>
+    <t>Artificial intelligence evolves with the development of computers even rely on computational development. The ways and processes of human thinking developed by Psychologists and welcomed by computational experts produce the science of Artificial Intelligence. This continues with the development of cognitive science that encourages the development of Artificial Intelligence to Cognitive Thinking Intelligence, a new pathway to the science of Artificial Intelligence that can emulate human cognitive abilities even if not 100%. Emulation of human cognitive abilities is developed based on the modeling of system interaction with the environment and information fusion, which can be used to conduct Inferencing, so when this occurs repeatedly it will produce knowledge that grows. This process is called Knowledge Growing System which is Brain Inspired Cognitive Artificial Intelligence and can be used for information extraction and when applied to instrumentation system will realize Intelligent Instrumentation System.</t>
+  </si>
+  <si>
+    <t>New Requirements of Teacher Professionalization for Emotional Labor and Psychological Capital in the Age of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Under the function of learning, research, politics and so on, the development of artificial intelligence education is very rapid. Artificial intelligence makes education precision further realized, which also puts forward new requirements for teachers’ specialization. Based on the relationship between education and traditional education in the era of artificial intelligence, this paper studies the strategies and high psychological capital that teachers need to have emotional labor, and puts forward some relevant suggestions, so that teachers can adapt to the new needs of this intelligent era.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence, Game Theory, Programming Used Languages and Platforms, Game Types and Training Methods</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence is one of the most sought-after branches of computer science today, and the branch of artificial intelligence tries to make machines act intelligently, enabling them to cope with more and more diverse problems on their own. Undoubtedly, one of the sectors that has the highest share in the development of artificial intelligence today is the computer games sector. The game development process has a more detailed structure every day. Artificial intelligence applications, which are a comprehensive information technology, have also affected game technologies closely. It is one of the most impressive works that are increasing day by day. Today’s computer games can even beat world chess champions and checkers. In this article, which started with this motivation, first of all, the definition of artificial intelligence was examined, and auxiliary calculation and training methods for artificial intelligence were introduced.</t>
+  </si>
+  <si>
+    <t>The Possibilities of Using Artificial Intelligence Technologies in Education and Science</t>
+  </si>
+  <si>
+    <t>This article discusses the practical implementation of artificial intelligence (ai) in education and scientific research. It provides examples of how and why ai is necessary and draws conclusions about how people's lives may change after ai is integrated into society.</t>
+  </si>
+  <si>
+    <t>Navigating the Future: The Role of Artificial Intelligence in Shaping Recruitment Practices</t>
+  </si>
+  <si>
+    <t>Effective human resources management (HRM) is crucial for all kinds of businesses in today's competitive environment since it improves organizational performance. This study aims to investigate how artificial intelligence (AI) is currently used in recruiting. A scoping review is a method used to look through the body of existing literature from different databases. Bias, which is otherwise becoming more prevalent in manual recruiting processes, is eliminated in recruitment through automation and analytics. Additionally, in conventional face-to-face interviews, candidates have been found to use impression management strategies. However, the impact of these strategies can be reduced with automated recruiting processes. Virtual interviews powered by AI minimize human bias. Additionally, it makes it easier for recruiters to find talent worldwide. Candidates' opinions of their workplaces and work surroundings are enhanced by stimulation. Using gamified methods, recruiters can determine if a prospect has the necessary work skills. The results and conclusions were practically exact in indicating that the best applications of technology may be found in the field of recruitment, where employing AI is favorable. The hiring process is more effective when AI is used. It minimizes repetitive tasks. The human resources (HR) team benefits from time savings. It is a very new development for HRM to use AI, and very few businesses have done so completely for all HR procedures. The main advantages of using AI will be increased productivity and automated repetitive work; nevertheless, the main challenge that businesses may have is their readiness to adopt innovative technology.</t>
+  </si>
+  <si>
+    <t>The Use of Artificial Intelligence Algorithms in Foreign Languages Teaching</t>
+  </si>
+  <si>
+    <t>The article is devoted to the analysis of the phenomenon of artificial intelligence and neural networks in the framework of foreign language education. The authors analyze the possibilities of these digital resources in foreign languages teaching. The article discusses current issues of the development and implementation of neural networks, describes their technical and technological characteristics for the educational content development. It has been identified and presented both the teaching and evaluating potential of neural networks in the practice of foreign languages teaching. It is presented the algorithm of software implementation in the form of an application. The authors analyze the existing tools of neural networks, the range of their capabilities in organizing feedback to students and the additional conditions that arise in this regard for mastering a foreign language. The article provides an algorithm for developing educational content based on neural networks for the development of all types of foreign language speech activity. They are given some methodological recommendations that describe the advantages and limits of using neural networks in the practice of foreign language education.</t>
+  </si>
+  <si>
+    <t>Comparative Analysis on Artificial Intelligence Technologies and its Application in FinTech</t>
+  </si>
+  <si>
+    <t>Universal technology has advanced with time, and as they say, “Necessity is the Mother of Invention,” this is impacting people's attitudes. As a result, people's attitudes regarding online networks have shifted from those of cable networks, which has steadily influenced the world's adoption of new technologies. Computerized Intelligence (AI). AI will enable financial businesses to totally rethink their business models, launch cutting-edge goods and services, and, most crucially, influence customer experience initiatives. In this second machine age, banks will face competition from nimble fintech startups that use cutting-edge technologies to supplement or even replace human labor with complex algorithms. Banking businesses will need to accept AI and use it into their business plan in order to keep a strong competitive advantage. As human selection is expensive, AI and ML are replacing human analysts in corporate tasks. Since AI is built on ML, it learns over time and provides the utmost accuracy in calculations and data analysis. AI also has the ability to introduce process automation to many industries as needed, as well as smart analytics and clear thought. AI-powered Chat-Bots have established themselves as a viable customer service tool, and because they save businesses time and money, they appear to be an uncomposable resource. The investments are a major part of the finance sector and taking in account of the investments prediction by the artificial intelligence algorithms and a comparison between them is the main motive behind this paper.</t>
+  </si>
+  <si>
+    <t>Development Trend and Thinking of Artificial Intelligence in Education</t>
+  </si>
+  <si>
+    <t>Artificial intelligence is a collection of information technologies based on big data and machine learning with intelligent capabilities. It integrates artificial intelligence into the field of education and uses key technologies and intelligent means in an intelligent education environment to optimize education development. The system promotes the synergy and integration of emerging intelligent technologies and the education industry. In general, the application of artificial intelligence in the field of education is constantly expanding and deepening, and the emergence of new concepts, new methods, and new ideas is bound to have a profound impact on the reform of the education industry.</t>
+  </si>
+  <si>
+    <t>Harnessing Artificial Intelligence to Promote Spiritual Intelligence Via Social Media</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence (AI) is redefining the paradigms of spiritual growth by harnessing the power of social media to promote Spiritual Intelligence (SI) in unprecedented ways. Through sophisticated algorithms and advanced data analytics, AI can curate personalized spiritual content that resonates deeply with individual users, fostering a more profound connection to inner consciousness and transcendent wisdom. By utilizing natural language processing, AI detects and amplifies trending spiritual themes, facilitating vibrant online communities dedicated to spiritual exploration and enlightenment. Machine learning models analyze user behavior to refine content delivery, ensuring that spiritual teachings and practices are accessible, relatable, and engaging. Furthermore, AI-driven chatbots and virtual guides provide round-the-clock support, answering spiritual queries and guiding users on their spiritual journey with unparalleled precision and empathy. This transformative synergy between AI and social media platforms transcends traditional barriers, democratizing spiritual wisdom and making it accessible to diverse audiences worldwide. By predicting and adapting to user needs, AI not only enhances personal spiritual growth but also cultivates a global culture of spiritual intelligence, unity, and collective consciousness, positioning itself as a formidable force in the evolution of human spirituality.</t>
+  </si>
+  <si>
+    <t>Research on Artificial Intelligence Visualization Application under Internet of Things Big Data</t>
+  </si>
+  <si>
+    <t>Machine learning is an inevitable outcome of the development of artificial intelligence research to a certain stage. It has become the most popular technology in the fields of computer vision and natural language processing. Learning techniques such as inductive logic programming, neural network-based connectionist learning technology, and statistical learning theory are constantly evolving. The shortcomings of various learning techniques in data representation and result processing have become a concern of many scholars. As one of the cutting-edge science and technology in the 21st century, artificial intelligence has a profound impact on education. This research is based on the artificial intelligence in Visualization Application for nearly 12 years. It has carried out visual analysis of research hotspots and frontiers. In addition, this study also discusses the research content through cluster analysis, discusses the influence of artificial intelligence on Chinese education field, and reflects on it.</t>
+  </si>
+  <si>
+    <t>Early Detection and Analysis of Lung Cancer Using Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>The revolutionary influence artificial intelligence (AI) has in revolutionizing lung cancer diagnosis is examined in this study report. The research explores the significant influence of artificial intelligence (AI) on many aspects of lung cancer diagnosis, highlighting its role in accuracy, efficacy, and early identification. The first section of the study explains how artificial intelligence has been used to diagnose lung cancer historically, from the first attempts in the 1960s to the most recent developments. It emphasizes the critical role AI plays in lung cancer screening using chest computed tomography (CT) and chest X-rays (CXR), demonstrating scientists’ unwavering dedication to advancing diagnostic capabilities. The paper devotes a large amount of space to the diagnostic efficiency attained by AI, showing an improvement in accuracy and a decrease in false positives. Multiparametric clustering analysis is made possible by the incorporation of AI recognition technology, which helps doctors with early-stage lung cancer screening. Additionally, the study explores the potential of AI to advance personalized medicine by detecting cancer at an early stage and customizing treatment based on patient-specific information. The study also looks at the more general applications of AI in lung cancer prediction, taking into account the complex interactions between immune cells, tumor cells, and cancer-related variables.</t>
+  </si>
+  <si>
+    <t>Embracing Artificial Intelligence in Higher Education: Opportunities and Challenges for a South African University of Technology</t>
+  </si>
+  <si>
+    <t>Artificial intelligence is a rapidly growing field of technology with the potential to significantly impact all aspects of our social interactions. Education currently uses AI to develop and evaluate innovative teaching and learning methods. This paper assesses the potential, opportunities, and challenges of integrating artificial intelligence (AI) within a South African University of Technology. The study looks at current trends and the literature to find the main growth drivers. These include rising demand for personalised and easy-to-acquire education, improvements in new technologies, and more money and investment. We provide practical recommendations for successful AI adoption, which include infrastructure development, curriculum integration, research ecosystem enhancement, student support services, ethical frameworks, and stakeholder engagement. By leveraging these strategies, the South African University of Technology can navigate challenges and capitalise on opportunities, ultimately advancing technological education and innovation in alignment with the socio-economic and cultural context of the African continent.</t>
+  </si>
+  <si>
+    <t>Digital Socio-Political Communication and its Transformation in the Technological Evolution of Artificial Intelligence and Neural Network Algorithms</t>
+  </si>
+  <si>
+    <t>The study aims to analyze the specifics of determining the subjects of digital social and political communication in the context of the development of artificial intelligence technologies and neural network algorithms. The work uses a case-study design. As a research methodology, the method of critical analysis of the digital communications practice in the socio-political sphere, as well as discourse analysis of modern scientific research in the field of the development of artificial intelligence and neural network algorithms, are used. It is concluded that the implementation of technological solutions based on artificial intelligence and neural network algorithms into the processes of socio-political communications creates a problem of defining the subject of communication acts in the socio-political sphere. Society may face such communication practices in which hybrid subjectness is realized. In the conditions of hybrid subjectness, both real subjects and programmed neural network algorithms acting as real subjects (but only imitating own subjectivity) interact in common communication space. The originality of the work lies in the formulation of the author's hypothesis about the emergence of the phenomenon of hybrid subjectness in the space of modern socio-political communications and its potential in the aspect of influencing the mass consciousness of citizens.</t>
+  </si>
+  <si>
+    <t>Future Trends in HRM: The Role of Artificial Intelligence and Automation in Shaping the Workplace</t>
+  </si>
+  <si>
+    <t>Artificial intelligence-based applications are integrated in the human resource management of firms for managing people within the region as well as international organisations. In the past years the growth of AI based applications proliferates the function of HR M that triggers to exciting new stream to study the effect of AI adoption on business level and individual outcomes. It evaluates the AI enabled HRM practises. The technology examines the firms with problem solving, decision making and utilisation of resources and opportunities for employees. The growing interest on AI based technologies for HRM for diffusion of innovation in large multinational enterprises. AI has the capability for reduction of administrative burden experienced by the HR Professional that allows them for precise decision making based on the data patterns. Adoption of artificial intelligence helps in effective employee management and decision making. So that employee of HR management can overcome the challenges. The study aims to analyse the future trends in HRM and the role of artificial intelligence and automation in shaping the workplace.</t>
+  </si>
+  <si>
+    <t>Educational Inclusion and its Meaning for the Achievement of Sustainable Development from the Use of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>In recent years, educational inclusion has acquired significant relevance in the global development agenda. As society grapples with complex and urgent challenges such as climate change, poverty and inequality, it is increasingly recognized that inclusive education plays a critical role in achieving sustainable development. In this context, Artificial Intelligence (AI) has become a powerful tool that can enhance educational inclusion and accelerate progress towards the sustainable development goals. The objective is to carry out an analysis about educational inclusion and its meaning for the achievement of sustainable development from the use of Artificial Intelligence (AI). The deductive method and exploratory research are used to analyze educational inclusion and sustainable development from Artificial Intelligence. It resulted in the implementation of various Parameters of considerations of excellence and quality in educational processes, concrete ways in which AI can help improve inclusive education and challenges and ethical considerations of implementing AI in educational inclusion. It is concluded that the need to promote policies and strategies that effectively integrate AI into educational systems, in order to achieve solid educational inclusion and move towards sustainable development. The importance of collaboration between governments, educational institutions, AI experts and society in general is underlined to ensure responsible and beneficial use of technology.</t>
+  </si>
+  <si>
+    <t>The Impact of Artificial Intelligence for Developing Supply Chain Collaboration Performance: An Empirical Investigation</t>
+  </si>
+  <si>
+    <t>Organizations are increasingly looking into artificial intelligence to improve operational efficiency and performance. Artificial intelligence marketing makes use of data to forecast customer behavior and improve their experience. It bridges the gap between data science and execution by processing and analyzing massive volumes of previously unmanageable data. An AI marketing tool is a platform or application that employs AI technology to enhance data-driven decisions. These technologies include combine artificial intelligence, and usual processing, by using machine learning, and data analytics to fasten the procedure with automatic processes, then analyze data, and give efficient output for optimizing the result for helping the management to frame new strategy for their business campaigns. This research will provide empirical information on how to maximize the benefits of AI capabilities for generating long-term SCP.</t>
+  </si>
+  <si>
+    <t>Workshop: Educational Innovation Through Generative Artificial Intelligence: Tools, Opportunities, and Challenges</t>
+  </si>
+  <si>
+    <t>The integration of Artificial Intelligence (AI) into the field of education is an unprecedented trend with the potential to revolutionize teaching approaches and significantly improve the overall learning experience. This workshop offers an opportunity for a strategic implementation of generative artificial intelligence in higher education, demonstrating its capacity to substantially enhance the creation and customization of digital educational materials. It is essential for educators to possess the capacity to utilize generative artificial tools, specifically when it comes to developing prompts for Large Language Models (LLMs). In addition to fostering a more interactive learning environment, these LLMs are driving the transition to educational systems that are more autonomous and adaptable. An in-depth exploration of the pragmatic and ethical aspects of AI implementation is undertaken to equip educators with the necessary knowledge and skills to employ AI in a responsible manner, thereby cultivating an engaging and equitable learning environment.</t>
+  </si>
+  <si>
+    <t>Identifying Patent Risks in Technological Competition: A Patent Analysis of Artificial Intelligence Industry</t>
+  </si>
+  <si>
+    <t>Identifying patent risks is a crucial way to assist technological innovation actor especially latecomers to confront with technological competition. The patent documents contained enormous and rich technical information to indicate patent risks and gain competitive advantage for both public and private sector entities in their marketplace. In this paper, we consider patent documents as objective data source and search them from INNOGRAPHY, a professional business database of intellectual property. The patent risks in technological competition were explored from the perspective of overseas patent layout, competition position of top assignees and top assignees holding high-strength patent based on patent analysis. The effectiveness of the approach is verified with the case study on artificial intelligence industry. The results showed that the U.K, Canada, Germany, the U.S. and Japan attached great importance to overseas patent layout. Regarding to the competition position of top assignees, assignees from the U.S., Japan, China and Korea were major competitors in artificial intelligence industry. The U.S. was the leader of artificial intelligence industry, holding 252 high strength patents. Although China had an obvious advantage over the number of patents compared to the U.S., Japan and other countries or regions in the field of artificial intelligence industry, China should be focused on expanding overseas patent layout and enhancing its competition position and high strength patents. This paper offers valuable contribution to the understanding of patent risks in technological competition in the artificial intelligence industry, and can be applied to various other technology industries and served as a starting point for developing more general models.</t>
+  </si>
+  <si>
+    <t>Research on the Application of Artificial Intelligence Technology in Teaching Introduction to Hotel Management in the Context of Smart Hotel</t>
+  </si>
+  <si>
+    <t>The rapidly developing information technology has made smart hotels one of the development trends in the hospitality industry. In the transition of pursuing digital transformation of hotel enterprises, artificial intelligence technology is increasingly applied to various fields of hotel services and management. The development of smart hotels and the application of artificial intelligence technology have put forward new demands and standards for hotel professionals. it is necessary to explore the role of artificial intelligence technology in the teaching of relevant courses in hotel management. Combining the construction of the course Introduction to Hotel Management and the analysis of the demand for talents from hotels under the background of the development of smart hotels, this paper explores the application of artificial intelligence technology in teaching Introduction to Hotel Management.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence in Air and Space Technologies: A Scientometric Analysis</t>
+  </si>
+  <si>
+    <t>The aim of this paper is to conduct a bibliometric analysis and evaluate publication trends of research papers related to artificial intelligence in air and space technologies for the last 50 years. The data was obtained from Scopus' database. The keyword for the search was “artificial intelligence“ “aerospace“ This paper seeks to identify top publishing authors, universities, countries, and reference articles to highlight collaboration between author., institutions, and countries in the region, and to gain insight into research topics that scholars have been working on recently. Moreover, distribution of publications according to their languages, document types, and research areas are evaluated. Articles from 1975 to 2023 were considered, and a total of 1.,111 artificial intelligence in air and space technologies-related publications were discovered. There were five main document types in artificial intelligence in air and space technologies related publications and conference paper and article were mostly used among all document types. The United States was found to be the most productive country and English was the most frequently used language among all publications. Furthermore., engineering is the main distribution channel, and it is followed by computer science and physics and astronomy as the top popular research areas.</t>
+  </si>
+  <si>
+    <t>Application Analysis of Artificial Intelligence Technology in Unmanned Driving</t>
+  </si>
+  <si>
+    <t>With the rapid development of artificial intelligence technology, artificial intelligence has been widely used in all walks of life. Unmanned driving is the mainstream of the future automobile industry. With the help of artificial intelligence, unmanned driving will gradually move towards real unmanned driving. Based on the concept of artificial intelligence technology and unmanned vehicle, combined with the current application status of unmanned vehicle, this paper analyzes the specific application of artificial intelligence in unmanned vehicle, and analyzes the problems existing in the application of unmanned vehicle at present, and looks forward to the development trend of unmanned vehicle in the future, which provides reference for the mature application of unmanned vehicle technology.</t>
+  </si>
+  <si>
+    <t>Impact of Artificial Intelligence in Basic General Education in Ecuador</t>
+  </si>
+  <si>
+    <t>The information and knowledge society leads to urgent changes in the world's educational systems. These changes must go hand in hand with new technologies and intangible services, education must focus their education for the jobs of the future. Education is one of the fundamental pillars in the advancement and progress of people, according to UNESCO, education can and should contribute to a new vision of sustainable world development. Artificial Intelligence in education currently offers a range of possibilities to both the teacher and the student in the teaching-learning process. According to UNESCO, Artificial Intelligence has the power to transform education. This article makes a study of Artificial Intelligence and how it is related to education; an analysis of the basic general education curriculum in Ecuador, as well as the importance of the use of tools based on Artificial Intelligence that contribute to strengthening the teaching-learning process.</t>
+  </si>
+  <si>
+    <t>AIMS5.0 AI Toolbox: Enabling Efficient Knowledge Sharing for Industrial AI</t>
+  </si>
+  <si>
+    <t>Industry 5.0 continues to reshape the industrial processes, the pivotal role of AI services in optimizing operations has become increasingly evident. Although the state-of-the-art AI models are widely employed across diverse application areas, the industrial sector faces numerous challenges in navigating through a plethora of the available AI models and libraries.Indeed, lacking effective employment guidelines for AI models can hinder their utility and decrease their adaption. This paper introduces the AIMS5.0 AI Toolbox, an innovative framework designed to address this challenge by fostering industrial knowledge sharing and distribution. The AIMS5.0 AI Toolbox serves as a comprehensive resource for industrial practitioners. It offers an integrated holistic platform for sharing models, tools, best practices, and guidance specifically directed towards the industrial AI-based consumers. Through its multifaceted approach, the toolbox facilitates seamless exchange of insights and expertise among the industrial actors. In addition, the AIMS5.0 AI Toolbox gives new ways to the process of fast prototyping by leveraging well-established AI-based models and libraries. By incorporating solid best practices and recommendations, the toolbox provides a structured framework for industrial users to harness the power of AI effectively.</t>
+  </si>
+  <si>
+    <t>Design and Implementation of Key Word Extraction System Based on Pre-Training Model and Artificial Intelligence Algorithm</t>
+  </si>
+  <si>
+    <t>With the rapid development of artificial intelligence technology in China, all walks of life have gradually integrated their advanced intelligent algorithm into it, and strive to improve the comprehensive operation efficiency. Based on the advanced technical characteristics of the pre-training model and the artificial intelligence algorithm, this study constructs the keyword extraction system model, in order to effectively improve the extraction efficiency and classification accuracy of keywords in the data resources. Combined with the empirical research and analysis, the design and implementation of the keyword extraction system based on the pre-training model and artificial intelligence algorithm effectively improves the accuracy of the keyword extraction, the error rate is further reduced, and the comprehensive operation stability of the system is significantly enhanced. Therefore, there is a positive relationship between the pre-training model, the application of the artificial intelligence algorithm and the design of the keyword extraction system. Based on the technical application of the pre-training model and the artificial intelligence algorithm, it is helpful to promote the operation efficiency and development quality of the keyword extraction system.</t>
+  </si>
+  <si>
+    <t>Optimizing University Teachers Learning Progress: Evolving Study Efficiency with Artificial Intelligence Agent</t>
+  </si>
+  <si>
+    <t>This paper explores using the COZE AI Agent platform to optimize university teachers’ learning progress and study efficiency. Key requirements like personalized learning paths, technology integration, and pedagogical innovation are identified. Testing evaluates the AI agent’s performance in generating tailored professional development recommendations. Results demonstrate improved study efficiency and professional growth through accurate, relevant advice. Limitations and prospects, including continuous feedback loops and data analysis, are discussed, highlighting AI agents’ potential to revolutionize professional development in higher education.</t>
+  </si>
+  <si>
+    <t>The Role of Artificial Intelligence Applications in Achieving Competitive Advantage for Business Organizations - Challenges and Proposed Solutions</t>
+  </si>
+  <si>
+    <t>The main principle of AI is to simulate and go beyond the way humans understand and interact with the world around us, which has quickly become the cornerstone of innovation. Artificial intelligence improves the performance and productivity of institutions by automating processes or tasks that previously required human strength, and the emergence of solutions and tools that rely on artificial intelligence means that more companies can benefit from artificial intelligence at a lower cost and less time. Hence, the adoption of competitive advantage (CA) is one of the most significant challenges for business organization management because of the urgent need to acquire a competitive advantage, depending on the extent to which the industrial sector can create a good working environment and formulate a strategy that supports innovation and its ability to respond to scientific progress and possess good knowledge and skills to achieve excellence in the internal and external environment. Therefore, the current research aimed to systematically analyze the scientific literature related to the application of artificial intelligence and machine learning (ML) in industry to achieve competitive advantage in business organizations. It has been shown that artificial intelligence has a positive impact on achieving competitive advantage in business organizations, and the research relied on The descriptive analytical approach to determine the framework to develop the proposed framework to clarify the relationship between artificial intelligence and competitive advantage in business organizations. An analysis of the literature on artificial intelligence and the competitive advantage of business organizations has been used to answer the main question of research: what is the role of artificial intelligence applications in achieving the competitive advantage of industrial business organizations?</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence Powered Fraud Detection and Prevention Analysis of Application of Machine Learning in Online Transactions in Banking</t>
+  </si>
+  <si>
+    <t>The inability of conventional techniques to keep up with changing fraudulent strategies has made the integration of artificial intelligence (AI) and machine learning (ML) in online banking fraud detection crucial. Real-time detection capabilities provided by AI-powered models improve the capacity to spot irregularities and questionable patterns that may indicate fraudulent activity. However, there are drawbacks, especially with deep learning models, such as issues with data quality, scalability, and transparency. The purpose of this paper is to assess the efficacy of AI in preventing fraud, offer performance-enhancing solutions, and discuss important deployment issues along with proposing a solution for AI integration. The study emphasises how AI-driven fraud detection systems must have strong data management, real-time adaptability, and transparency.</t>
+  </si>
+  <si>
+    <t>Explainable Artificial Intelligence for Deep Synthetic Data Generation Models</t>
+  </si>
+  <si>
+    <t>Artificial intelligence encapsulates a "black box" of undiscovered knowledge, propelling the exploration of Explainable Artificial Intelligence (XAI) in generative data synthesis and deep learning. Focused on unveiling these "black box" areas, pointed into interpretability and validation in synthetic data generation, shedding light on the intricacies of generative processes. XAI techniques illuminate decision-making in complex algorithms, enhancing transparency and fostering a comprehensive understanding of non-linear relationships. Addressing the complexity of explaining deep learning models, this paper proposes an XAI solution for deep synthetic data generation explanation. The model integrates a clustering approach to identify similar training instances, reducing interpretation time for large datasets. Explanations, available in various formats, are tailored to diverse user profiles through integration with language models, generating texts with different technical detail levels. This research contributes to ethically deploying AI, bridging the gap between advanced model complexities and human interpretability in the dynamic landscape of artificial intelligence.</t>
+  </si>
+  <si>
+    <t>Classification in Rice Genome using Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Epigenetic modifications, like N6methyladenine (6 mA), regulate genetic configuration and impact the cellular tasks. Recognizing the dissemination of 6mA sites within the rice genome is required for deciphering its influence on plant progression. In the proposed work, a detailed investigation of 6 mA sites in the rice genome using advanced artificial intelligence (AI) techniques. In this research AI models are trained on vast genetic data to correctly categorize 6 mA sites. The classification result has shown the detailed useful implication of 6 mA adjustments, shedding light on possible controlling elements and their roles in important biological procedures.</t>
+  </si>
+  <si>
+    <t>Computer Network Security Technology Based on Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>As artificial intelligence (AI) technology continues to develop, cybersecurity issues are becoming increasingly prominent. Improving computer network security can further enhance the security of computer network information and avoid being affected by external environments. Applying AI technology to computer network security work can enhance the security of computer network information data, prevent illegal elements from illegally stealing and deleting computer network information data, and play a positive role in computer network security work. This article implemented the application of AI technology in computer network security through network security design, intrusion detection technology, and network security management technology based on AI technology. 82575 pieces of data were collected as data samples. To more accurately evaluate the actual effectiveness of AI in intrusion detection technology, it has been proven that AI has a very good effect in the utilization of computer network security technology.</t>
+  </si>
+  <si>
+    <t>Integrating Artificial Intelligence and Multiple Intelligences for Advanced Educational Models</t>
+  </si>
+  <si>
+    <t>The aim of educational innovation is to foster students' creative and problem-solving skills via the integration of several disciplines, including science, technology, engineering, art, and mathematics. Efficiently identifying and fostering the various abilities of pupils continues to be a crucial obstacle. This research presents a sophisticated educational approach that combines the notion of multiple intelligences with artificial intelligence (AI) technology to tackle this problem. This concept improves the teaching environment by including intelligent auxiliary services for instructors and students via the use of smart speech and picture interaction. Artificial intelligence (AI) integrated into the multiple intelligence’s framework enables the ability to observe, analyze, and implement personalized teaching tactics in real-time using machine learning. The suggested AI-assisted education paradigm aims to enhance teacher-student interactions and facilitate personalized instruction. The study provides evidence that this technique successfully facilitates personalized and captivating learning experiences, promoting students' diverse talents and augmenting their creativity and problem-solving capabilities. This approach seeks to fundamentally transform conventional educational techniques by addressing the disparity between existing educational practices and the future requirements of the workforce.</t>
+  </si>
+  <si>
+    <t>Research on the improvement of English cognitive linguistics under computer artificial intelligence technology</t>
+  </si>
+  <si>
+    <t>In the spoken dialogue scene of English cognitive linguistics under artificial intelligence technology, we use artificial intelligence technology to construct different forms of virtual reality scenes. In the artificial intelligence English learning scenario, students can obtain real-life English cognitive linguistics oral dialogue training. During the training process, the artificial intelligence technology can record the students’ English cognitive linguistics oral dialogue voice information and play back the dialogue voice information to the students. The artificial intelligence technology enables the students to know whether their pronunciation in the English cognitive linguistics oral dialogue is not correct.</t>
+  </si>
+  <si>
+    <t>The Challenge of Copyright Protection of Artificial Intelligence Products to the Field of Intellectual Property Legislation Based on Information Technology</t>
+  </si>
+  <si>
+    <t>The rise of artificial intelligence plays an important role in social progress and economic development, which is a hot topic in the Internet industry. In the past few years, the Chinese government has vigorously increased policy support to promote the golden age of artificial intelligence. However, with the rapid development of artificial intelligence, the copyright protection and intellectual property legislation of artificial intelligence products have brought some challenges.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence as a booster of a Business Intelligence System to help the recruitment process : Business Intelligence, Human Resources and Talent</t>
+  </si>
+  <si>
+    <t>This article aims to better understand how the process of Recruitment and Selection works in the area of Human Resource Management, having as a key tool and differentiator, Artificial Intelligence (AI). The Human Resources area has currently been evolving towards the application of AI in the Recruitment and Selection process (R&amp;S), with the purpose of restricting fields of competencies or skills and optimizing time in data analysis. AI, on the other hand, has had a huge expansion in the last years, in several areas. Because it is an advantageous tool, many organizations are already starting to adopt this method in order to enhance their organization internationally (thus revealing AI to be a key tool). This transformation in organizations, with the application of AI, is mainly the result of data that are generated in Information Systems, often entered by the candidates themselves at the time of Recruitment.</t>
+  </si>
+  <si>
+    <t>Comprehensive Study on Heart Disease Prediction and Risk Stratification using Explainable Artificial Intelligence Technique</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence (AI) is becoming increasingly important in healthcare, particularly in identifying heart disease and predicting its occurrence. This article discusses how Explainable AI (XAI)-based methods are employed to assess the risks of heart disease and predict its risk stratification. The primary goal is to address the ‘black-box’ issue associated with older AI models by clarifying their decision-making processes. Other XAI methods discussed in this research include Shapley Additive Explanations (SHAP), Local Interpretable Model-agnostic Explanations (LIME), Layer-wise relevance Propagation, Partial Dependency Plots (PDP), and Gradient-Class Activation Map (Grad-CAM) method, employed for heart disease prediction and its risk stratification. Additionally, this paper discusses XAI methods that are specific to neural networks and tree-based models. Many people can better comprehend AI models using XAI, which is crucial for clinical applications. Furthermore, this paper highlights research gaps in combining XAI with Electronic Health Records (EHR) and real-time data analytics. The Dense-Net classifier method achieves an accuracy of 99.8%, recall of 98%, and F1-score of 99.8%, outperforming existing methods such as Random Forest and Extreme Boost (XG-Boost).</t>
+  </si>
+  <si>
+    <t>Application Analysis of Artificial Intelligence Technology in the Development of Mobile Internet</t>
+  </si>
+  <si>
+    <t>Mobile Internet is a new service that obtains services and services through intelligent mobile terminals and mobile wireless communication. It is the general name of activities that combine and practice Internet technology, platform, business model and application with mobile communication technology. Artificial intelligence technology exerts its advantages in application universality, autonomy and iteration, and effectively solves the problems of data organization and environment, so as to build a more stable and rigorous model. In the information age, the pace of people's life is quickening, and the PC Internet is far from meeting people's needs. Users are eager to enjoy convenient network information services anytime and anywhere. Starting with artificial intelligence technology, the author analyzes the important application of artificial intelligence technology in the development of mobile internet, which promotes the development of internet in our country.</t>
+  </si>
+  <si>
+    <t>The Use of Artificial Intelligence Tools in Developing Curricula for University Students in Jordan</t>
+  </si>
+  <si>
+    <t>This study aims at investigating the applicability of Artificial Intelligence (AI) tools in approaching significant issues confronting universities curriculum in Jordan specifically a setting with different institutional structure and amount of resources. AI tools are celebrated internationally for enhancing the potential to redesign curriculum as innovative pedagogy, promoting adaptiveness and develoing student-centric educational delivery system. Through scrutinizing the use of AI in curriculum, this study offers a broad understanding of how these technologies can help to close the gap between academic preparation and the current dynamic organizational environment. To this end, a quantitative cross sectional survey was administered on 120 students from the public and private universities in Jordan. The data suggest that AI increases the subject relevance of academic content, helps to personalize the content, and encourages students. Also, AI was discovered to help in ensuring that the proficiency acquired by the learners was relevant to the existing employment sector nationally and globally. Nevertheless, the results reveal key challenges that prevent its use, including data privacy issues, lack of resources, and faculty development. All these factors form hurdles that are a burden to the integration of these AI tools in the Jordanian higher education system. This study calls for innovative funds in new technologies, a faculty institute, and a partnership between the academic world and other sectors. It would thus enable the Jordanian university-full harness the potential of AI- to transform its curricula and improve the quality of higher learning. The present research work provides a plan for the policymakers and the educators for the AI implementation in the higher learning institutions in Jordan and focuses on practicalities of AI adoption.</t>
+  </si>
+  <si>
+    <t>Bridging Healthcare Disparities in Rural Areas of Developing Countries: Leveraging Artificial Intelligence for Equitable Access</t>
+  </si>
+  <si>
+    <t>Electronic Healthcare disparities in rural areas have been a persistent concern, with limited access to quality healthcare services worsening the challenges faced by rural populations. This paper engages in a comprehensive review that explores the persistent issues of healthcare disparities in rural areas and explores the potential of Artificial Intelligence (AI) to mitigate these challenges. It emphasizes the need for infrastructure development, particularly robust internet connectivity, to support the adoption of AI in rural healthcare. Training and education for healthcare professionals are highlighted as crucial for effective AI utilization. The paper underscores the importance of data quality and availability, suggesting that initiatives and interoperability can enhance healthcare data in rural settings. Cost-effective AI solutions tailored to the specific needs of rural healthcare are identified as essential for overcoming financial constraints. Regulatory support is recognized as a key factor in simplifying compliance requirements for integrating AI into rural healthcare practices. The paper concludes by highlighting the practicality of these solutions and their potential to leverage AI for improving healthcare access in rural populations.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence And Internal Control: A Perspective of Chinese Enterprises</t>
+  </si>
+  <si>
+    <t>Based on the theories of artificial intelligence and internal control, this paper analyses the important roles of artificial intelligence technology in enterprise internal control. The purpose of the study is to offer a certain reference for the development of enterprise internal control. We want to expound the advantages of artificial intelligence technology so as to study the practical application strategy of artificial intelligence in enterprise internal control. The technology of artificial intelligence is used to optimize some processes in people's production and life. The current trend of AI development has a good application prospect in all walks of life.</t>
+  </si>
+  <si>
+    <t>Big Data and Artificial Intelligence: Revolutionizing Business Decision-Making</t>
+  </si>
+  <si>
+    <t>The term artificial intelligence (AI) refers to the fourth industrial revolution. Globally, artificial intelligence and big data have revolutionized all sectors. Artificial intelligence has grown into a revolutionary technology with profound implications on many industries, included business, thanks to the usage of big data. Artificial intelligence (AI) and big data has transformed decision-making procedures in the past few years by giving businesses access to sophisticated analytical tools that let them glean insightful information from massive volumes of data. Artificial intelligence segments machine learning and deep learning have been extensively utilized to tackle and enhance a wide range of business issues, including marketing, credit card fraud detection, algorithmic trading, customer support, demonstrating products according to consumer preferences, and insurance underwriting. Using AI and big data into marketing techniques may help a business owner boost audience response and create a powerful online brand that can compete with competitors. Examining how big data and decision-making are used in artificial intelligence applications in business settings is the main objective of the research. In specifically, this research looks at how artificial intelligence is being used to improve decision-making processes and how that's affecting corporate structures. According to the report, artificial intelligence plays a revolutionary role in business decision-making, providing a host of benefits related to effectiveness, precision, and creativity.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence in The Integration Of Education, Science And Practice</t>
+  </si>
+  <si>
+    <t>This article is the preliminary stage of data presentation about artificial intelligence, an upcoming issue today. What is artificial intelligence in the article? The importance of artificial intelligence in education, science, and integration is addressed. One of the hottest topics in the present world is artificial intelligence. How will the artificial intelligence revolution affect humanity in the future? Will it have a future raises open questions? We want to remind you of another aspect of the time on artificial intelligence touch through literature, education, science, and practice integration, and it will dwell upon the importance and role of artificial intelligence that we found opposite. The author(s) provide short information concerning the above topic before delving into the discussion of artificial intelligence.</t>
+  </si>
+  <si>
+    <t>Role of Emotional and Artificial Intelligence on Employee Performance in Service Industry: A Review of Literature</t>
+  </si>
+  <si>
+    <t>Artificial intelligence combined with the emotional intelligence are emerging as the primary game changers in the industry 4.0. Over the last two decades, the literature has focused on emotional intelligence as a human intelligence and artificial intelligence as an intelligent machine. To ensure future growth, an organisation looks to technological advances for support, but should still remain focused on developing the people resources that power the organisation and drive it forward by focusing on the two. Given the significance of these concepts in the DisRUPT business environment, the authors have made an attempt to examine their impact on employee performance. Thus, this conceptual research through the review of literature investigates the impact of Emotional and artificial intelligence (AI) on employee performance, particularly in the context of service industry.</t>
+  </si>
+  <si>
+    <t>Optimal Allocation of Power Grid Human Resources Based on Artificial Intelligence Technology and Fuzzy Neural Network</t>
+  </si>
+  <si>
+    <t>The most important task of power supply company is power grid operation management. Up to now, the development of China's power grid has entered an intelligent era, and the reason for this phenomenon lies in the formation of the new power grid operation and management system. In this case, enterprise leaders must put more energy into human resource management, otherwise the development of the company is difficult to be closely related to this period. Therefore, in order to realize the efficient and intelligent optimal allocation of human resources in power grid, this paper proposes a resource optimal allocation algorithm based on deep data generation and fuzzy neural network to predict the resource demand at a certain time in the future. The algorithm is based on fuzzy neural network for resource data mining and analysis, and on this basis, the network is refined by particle swarm optimization algorithm. The results of numerical experiments show that the prediction error of this algorithm for human resource demand of power grid enterprises is 0.13%, which is 2.84% lower than that of using fuzzy neural network only. Machine learning algorithm, which has been proved to have better overall performance.</t>
+  </si>
+  <si>
+    <t>The Application of “Internet+” Artificial Intelligence in Computer Network Technology</t>
+  </si>
+  <si>
+    <t>This paper discusses the application of “Internet +” artificial intelligence in computer network technology. With the development of science and technology, human beings have entered the Internet era, which has changed the traditional way of learning and working, and largely promoted social development. At the same time, the rapid development of artificial intelligence technology, its use in computer network technology, can play an effective role. Firstly, we introduce the content related to artificial intelligence and big data technology, then analyze the advantages of applying it in computer network technology, and finally put forward effective strategies.</t>
+  </si>
+  <si>
+    <t>Systematic Review on Humanizing Machine Intelligence and Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>In this era, Machine Learning is transforming human lives in a very different way. The need to give machines the power to make decisions or giving the moral compass is a big dilemma when humanity is more divided than it has ever been. There are two main ways in which law and AI interact. AI may be subject to legal restrictions and be employed in courtroom procedures. The world around us is being significantly and swiftly changed by AI in all of its manifestations. Public law includes important facets such as nondiscrimination law and labor law. In a manner similar to this when artificial intelligence (AI) is applied to tangible technology like robots. In certain cases, artificial intelligence (AI) might be hardly noticeable to customers but evident to those who built and are using it. The behavior research offers suggestions for how to build enduring and beneficial interactions between intelligent robots and people. The human improvement is main obstacles in the development and implementation of artificial intelligence. Best practices in this area are not governed by any one strategy that is generally acknowledged. Machine learning is about to revolutionize society as it is know it. It is crucial to give intelligent computers a moral compass now more than ever before because of how divided mankind is. Although machine learning has limitless potential, inappropriate usage might have detrimental long-term implications. It will think about how, for instance, earlier cultures built trust and improved social interactions via creative answers to many of the ethical issues that machine learning is posing now.</t>
+  </si>
+  <si>
+    <t>Analysis and Guidance for Standing Broad Jump Based on Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>In this paper we propose and implements a standing long jump movements analysis algorithm based on artificial intelligence to help students improve their performance. We select the BlazePose, a lightweight neural network under the Mediapipe framework for human pose estimation. We extracte the coordinate information of body joints with Mediapipe, and use the extracted coordinate information to design the algorithm of standing long jump action segmentation and key frame selection for quantitative analysis movements. To evaluate the effectiveness of the project, we recruit 24 students to attend the Experiments with two rounds of tests, Experiment results show that the proposed algorithm can automatically detect and identify problems and deficiencies in key movements, and give suggestions for improvement. By analyzing the data of jumpers' take-off skills, posture control and landing methods, we can provide suggestions to help them improve their skills and performance.</t>
+  </si>
+  <si>
+    <t>Application Review of Artificial Intelligence in Superconducting Devices</t>
+  </si>
+  <si>
+    <t>Superconducting device has revolutionized various fields, with applications ranging from medical imaging to power transmission. However, further advancements require addressing challenges related to efficiency, reliability, cost, and complexity. Artificial intelligence (AI) offers promising solutions to these challenges, enabling the development of more efficient, reliable, and cost-effective superconducting systems. This paper introduces the recent advances of AI in superconducting device, such as magnetic imaging (MRI), superconducting cable and superconducting motor. Several challenges hinder the widespread adoption of AI in applied superconductivity, such as benchmark models, real-time inference, and community acceptance, are proposed. By addressing these issues, AI’s transformative power will unlock new possibilities, leading to ground-breaking advancements and widespread applications across various fields of superconducting devices.</t>
+  </si>
+  <si>
+    <t>Examining the Impact of Artificial Intelligence Ethical Issues on Managerial Accounting Performance Metrics</t>
+  </si>
+  <si>
+    <t>This abstract attempt to explore the extent to which ethical issues impact the managerial accounting performance indices due to the incorporation of AI. There is a question about bias, which increases the adoption of AI technologies in managerial accounting and may affect the reliability of accountants' metrics as well as the issues of accountability and transparency. This is because, in the current world business environment, which features globalization, high-level transparency and antagonism, it is important to apply new information technologies like AI. The study launched on a sample of 200 bookkeepers of Romania who used AI for managerial accounting revealed that the ethical concerns related to confidence, accountability, and autonomy significantly influence AI functioning and application.</t>
+  </si>
+  <si>
+    <t>Enhancing Mental Health With Artificial Intelligence Current Trends and Future Prospects</t>
+  </si>
+  <si>
+    <t>The element of wellness is usually far beyond one’s reach as services go out of people’s hands in most proportions of the world populations. Due to stigma, lack of sufficient trained professionals, high prices, mental health care is basically unavailable. That means that millions have a disorder of depression or anxiety without good treatment options. AI today promised solutions in diagnosis AI platforms offer clinicians data driven insights to improve treatment options, while tools like chatbots and virtual assistants provide accessible, cost effective support, reducing reliance on therapists. This paper establishes a scalable, secure, and user friendly AI system capable of being integrated into any mental health framework.</t>
+  </si>
+  <si>
+    <t>The Impact of Artificial Intelligence on Law Students: Opportunities, Challenges, and Adaptation Strategies</t>
+  </si>
+  <si>
+    <t>This literature review aims to synthesize existing research on the opportunities, challenges, and best practices for incorporating AI into legal education. By analyzing the transformative potential of AI, effective strategies for AI integration, and implications for the roles and competencies of future lawyers, this review provides insights and recommendations for law schools navigating the AI-driven future. The findings suggest that AI presents significant opportunities to enhance legal education, such as personalized learning experiences, practical skill development, and exposure to real-world legal technology applications. However, successful AI integration also poses challenges, including curriculum redesign, faculty training, and ethical considerations.</t>
+  </si>
+  <si>
+    <t>Creating a Novel Approach to Examine How King Saud University’s Arts College Students Utilize AI Programs</t>
+  </si>
+  <si>
+    <t>One of the cutting-edge ideas that is essential to improving students’ behavioral intention for using artificial intelligence (AI) and attitude toward it (ATAI) at higher education institutions is artificial intelligence learning. Artificial intelligence education is not widely available in Saudi Arabian universities. The study’s goal is to ascertain how perceptions of assessment quality, perceived risk, price value, artificial intelligence anxiety, educational quality, and perceived AI intelligence affect attitudes toward and perceived usefulness of employing artificial intelligence. When attempting to encourage the use of artificial intelligence (AI) in higher education, take into account factors such as perceived utility, attitude toward AI, behavioral intention to use, user happiness, and general mindset regarding AI. Additionally considered is the mediating function that behavioral intention and user pleasure have when utilizing artificial intelligence (USAI). A survey of Saudi universities was conducted in order to meet the study’s goal. 183 questionnaires were distributed around the universities to collect student data. Partial least squares (PLS) analysis and structural equation modeling were utilized to examine the data once it was gathered. User satisfaction in using artificial intelligence is the most crucial element in promoting student adoption of AI in higher education ( β=0.646 , t-value = 10.402). Perceived usefulness of using artificial intelligence ( β=0.309 , t-value = 4.240; β=0.275 , t-value = 2.194; and β=0.473 , t-value = 7.619, respectively) and attitude toward artificial intelligence ( β=0.285 , t-value = 2.584; and β=0.151 , t-value = 2.453, respectively) are significant factors in transferring the positive effects of behavioral intention to use and user satisfaction in using artificial intelligence. A crucial part of communicating the positive impacts of AI adoption in higher education is ...</t>
+  </si>
+  <si>
+    <t>The Language Model Revolution: LLM and SLM Analysis</t>
+  </si>
+  <si>
+    <t>As technology develops day by day, significant developments have been made in the field of artificial intelligence (AI). In particular, machine learning (ML) and deep learning (DL), as the main technologies that form the basis of artificial intelligence, have offered revolutionary innovations and laid the foundation for future technologies. Traditional artificial intelligence models are based on algorithms that show high performance in certain tasks such as classification, scoring, prediction, and pattern recognition. These algorithms are developed to best perform a specific task, making it difficult for artificial intelligence to be sufficiently effective in areas that require flexibility. Generative artificial intelligence, which has become widespread in recent years, has the ability to produce certain types of content in addition to the competencies of traditional artificial intelligence models. This has revolutionized the field of productivity in artificial intelligence. Generative artificial intelligence language models have gone beyond the limitations and started a new era in artificial intelligence applications. Where traditional artificial intelligence models are limited, language models have come into play, especially with their natural language processing (NLP) capabilities. Rather than just analyzing data, language models can learn the rules of the language and provide human-like responses, produce text, and offer a wider range of applications. In this way, artificial intelligence systems have become more flexible, extensible, and dynamic. With the rise of language models in this field, concepts such as large language models (LLM) and small language models (SLM) have emerged. Large language models have come to the fore as systems that can provide deep knowledge and language production on a wide variety of topics by being trained on huge data sets. Large language models such as ChatGPT are one of the most common and impressive examples in this field. However, small language models, which are smaller and specialized language models, have begun to be used as an alternative to large language models in certain areas because they require less data and processing power. Small language models stand out with their lighter but targeted performance, offering effective solutions, especially in situations where there are resource limitations. At this point, using both large and small versions of language models in the right scenarios provides great advantages in terms of sustainability and efficiency. This study aims to reveal the transformative effect of technology on artificial intelligence and the critical role of language models in this process by evaluating language models and the issues to be considered in the selection of these models.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence Inclusion in Landslide Monitoring</t>
+  </si>
+  <si>
+    <t>In order to effectively harness technological innovation for sustainable development, this article offers insights and recommendations for future actions. Over the past several years, landslides become a major natural hazard which causes a large amount of damage. With the deployment of Artificial Intelligence (AI) in landslide monitoring in recent years. In the current study the early warning system for AI and ANN becomes widely used domain. Landslide susceptibility is considered as a major aim for monitoring of landslide. Learning process for AI in landslide monitoring have been focused strictly. The factors influencing Landslide monitoring using AI has been discussed. Finally based on the analysis the future suggestion has been provided and a framework is recommended.</t>
+  </si>
+  <si>
+    <t>Optimization and Implementation of Concrete Compressive Strength Prediction Framework Using Artificial Intelligence Classifiers</t>
+  </si>
+  <si>
+    <t>Concrete compressive strength (CS) plays a very vital role in selection of material for various purposes and matter ofconcern, in reference to this there is always a big confusion in terms of which tools to be used in order to predict correct using artificial intelligence (AI), with the evolution of AI in recent years, to predict CS of concrete various ML techniques are in trend to be used. AI is a broader term initializing various learning models and used human intelligence incorporated with machine intelligence. Different learning models can be used depending upon various types of data set and formulation. Various data sets have to be classified on various parameters and aggregated by significant domain. On the other hand, numerical data sets can be empirically used and can be evaluated on basis of regression and depends upon relationship between two variables. Some of the data sets are required to be divided into clusters so that they can be more useful and free from deformities. However clustering technique is useful when various data sets are combined together and not separable. In Civil applications, quality of concrete has to be identified and checking using numerical model and regression technique has to be followed. In this paper the results are calculated for eleven various sub classifiers considering seven various parameters including accuracy, error, TP rate, FP rate, F measure, MCC and AUC</t>
+  </si>
+  <si>
+    <t>A Scientometric Study of Artificial Intelligence in the Health Care Sector</t>
+  </si>
+  <si>
+    <t>The increasing application of Artificial Intelligence usage in health care and medicine has attracted considerable research interest in the recent past. The objective of this paper was to provide a scientometric analysis of artificial intelligence in the healthcare sector. The momentum gained by artificial intelligence and information technology gave impetus and importance to health care. The researchers used the Scopus database to extract the papers. VosViewer tool was employed for advanced analysis, whereas Microsoft Excel was used in depicting graphical representation. The study summarises the research conducted by different authors, various universities and countries to extend the benefits of artificial intelligence to healthcare. This paper would be of some help to practitioners and researchers in the healthcare sector to know more about AI in healthcare.</t>
+  </si>
+  <si>
+    <t>Research on the Application of Artificial Intelligence Technology in Economic Management in the Information Age</t>
+  </si>
+  <si>
+    <t>With the rapid development of information technology and Internet technology, artificial intelligence (AI) innovation technology has made breakthrough progress, which has important impact and significance for economic society. By analyzing four economic effects of AI, including intelligent penetration effect, boundary extension effect, knowledge creation effect and self-deepening effect, this paper probes into the main factors of artificial intelligence affecting economic growth, specifically from three angles of labor factor, capital factor and production technology. In addition, this paper also empirically tests the relationship between artificial intelligence and economic growth according to three important indicators of artificial intelligence, such as industrial scale, patent number and financing scale, and further demonstrates the significant impact of artificial intelligence on economic growth.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence and its Effectiveness in Modern Teaching</t>
+  </si>
+  <si>
+    <t>Artificial intelligence (AI) is not a new term; its beginnings go back to the beginnings of the fifth decade in the year 1955. Since the emergence of artificial intelligence, it has been in the process of continuous development and spread of its technologies, until it recently reached the most prominent application, which is the ChatGPT program. AI technology is one of the most important modern technologies that contribute to the development of many fields, raise the level of quality, improve productivity, and increase efficiency. Education is one of the most important areas affected by modern technologies, which moved education from the ordinary level to the level of creativity and innovation. The idea of this research comes from several reasons: 1- The rapid transfer of education to a larger world in a short period, 2- The many positives that artificial intelligence had and acquired; 3- The need for the teacher to develop himself in this field and keep pace with the modern era, 4- The absence of motivation among many students, and the infiltration of boredom and lethargy among their ranks. 5- The need for the courses taught by the student to adapt technology in this era, and the inclusion of artificial intelligence completes that. 6- Enriching the research library with a study related to the important topic needed by the teacher and the student. 7- The limited thinking of some students and the lack of scientific communication and its stopping at a certain point.</t>
+  </si>
+  <si>
+    <t>A Review on Various Artificial Intelligence Techniques Used for Transmission Line Fault Location</t>
+  </si>
+  <si>
+    <t>Transmission line fault location has been estimated using various methods such as conventional distance relaying, differential relaying, artificial intelligent (AI) methods etc. Among all the methods AI based methods locates fault more accurately than others. In this work various AI methods used for transmission line fault location has been discussed with their advantages and limitations. Different AI methods that have been discussed are nearest neighbor algorithm, linear regression, logistic regression, artificial neural network, support vector machine, decision tree. With the various advantages of AI methods, it can be used effectively for locating faults in transmission lines.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence in Science and Society: The Vision of USERN</t>
+  </si>
+  <si>
+    <t>The recent rise in relevance and diffusion of Artificial Intelligence (AI)-based systems and the increasing number and power of applications of AI methods invites a profound reflection on the impact of these innovative systems on scientific research and society at large. The Universal Scientific Education and Research Network (USERN), an organization that promotes initiatives to support interdisciplinary science and education across borders and actively works to improve science policy, collects here the vision of its Advisory Board members, together with a selection of AI experts, to summarize how we see developments in this exciting technology impacting science and society in the foreseeable future. In this review, we first attempt to establish clear definitions of intelligence and consciousness, then provide an overview of AI’s state of the art and its applications. A discussion of the implications, opportunities, and liabilities of the diffusion of AI for research in a few representative fields of science follows this. Finally, we address the potential risks of AI to modern society, suggest strategies for mitigating those risks, and present our conclusions and recommendations.</t>
+  </si>
+  <si>
+    <t>Short Paper: Development of Production Planning and Control through the Empowerment of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Due to the significant increase in market dynamics and constantly changing circumstances, manufacturing companies are facing increasing pressure. This is expressed in volatile demand and shorter product life cycles, which place complex requirements on production. Production planning and control, as the linkage of internal value creation with external requirements and input from external suppliers, has a significant influence on the production and is therefore the key enabler for the economic success of manufacturing companies. In order to address the high complexity in production planning and control, digitization of manufacturing and techniques of Artificial Intelligence offer great potential for further development of production planning and control. This paper presents a stage-based maturity model that describes the development of production planning and control through the utilization of digital technologies and Artificial Intelligence. Furthermore, the paper explains which potentials both fields offer at individual maturity stages of production planning and control in order to improve planning results.</t>
+  </si>
+  <si>
+    <t>Computer-aided Translation in the Context of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>With the rapid development of modern science and technology, especially computer technology, artificial intelligence and many traditional scientific domains have gradually realized integration. Computer-aided translation technology will greatly improve the translation efficiency and reduce the cost of translation, so it is gradually favored by all walks of life. Based on this, the paper reviews the development trend of computer-aided translation, introduces the process of computer-aided translation in detail, and summarizes its advantages and disadvantages aiming to provide some references for the study of computer-aided translation. In addition, the study of computer-aided translation in the Context of artificial intelligence also has a certain enlightening effect on interdisciplinary research.</t>
+  </si>
+  <si>
+    <t>The Application of Big Data and Artificial Intelligence Technology in Football Training and Competition</t>
+  </si>
+  <si>
+    <t>With the rapid development of science and technology, the application of big data and artificial intelligence (AI) in sports is becoming more and more extensive, providing new perspectives and methods for football teaching and training. AI and big data collect and analyze a large amount of data and then build models, which can be used to evaluate the level of football players, formulate technical and develop training strategies. This article analyzes cases in order to explore how to use big data and AI to optimize football training, competition, and refereeing. Practical suggestions can also be put forward through the difficulties faced by big data and artificial intelligence technology. Finally, with these technologies, football will develop into a scientific, intelligent, and popular future.</t>
+  </si>
+  <si>
+    <t>Prototyping an Explainable Artificial Intelligence Model (XLSM) for Forecasting the Bitcoin Price</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence (AI) significantly improves time series forecasting in the financial market, yet it is challenging to establish reliable real-world finance applications due to a lack of transparency and explainability. This paper prototypes an eXplainable Long Short-Term Memory (XLSTM) model to train and forecast the price of Bitcoin using a group of 11 determinants. The results show good performance in price forecasting as measured by a mean absolute percentage error (MAPE) of 2.39% and an accuracy of 89.54%. Additionally, the AI model explains that trading volume and prices (Low, High, Open) contribute to the price dynamics, while oil and Dow Jones Index (DJI) influence the price behavior at a low level. We argue that understanding these underlying explanatory determinants may increase the reliability of AI’s prediction in the cryptocurrency and general finance market.</t>
+  </si>
+  <si>
+    <t>Research on Development and Challenges of Chinese Medical Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Medical artificial intelligence is the research focus and development orientation of China's current health informationization. Medical artificial intelligence can transform and upgrade modern medical service industry as well as promoting the innovation and development of health industry constantly. In July 2017, the State Council of China issued the “New Generation Artificial Intelligence Development Plan”, which proposed to promote the application of the new modes and new methods of artificial intelligence treatment in smart health care, establishing precise smart medical system and comprehensively improving the intelligent level of health industry, including, specifically, the development of human-machine coordination surgical robots, intelligent diagnosis and treatment, the R&amp;D of a physiological monitoring system which is wearable and biocompatible and the R&amp;D of programs on human-computer collaborative clinical intelligent diagnosis and treatment, so as to realize the intelligent image recognition, pathological classification and intelligent multidisciplinary consultation, promote intelligent medical supervision and strengthen epidemiological intelligence surveillance and prevention. However, the development of China's medical artificial intelligence technology will bring both new opportunities and new challenges in the meantime. This paper analyzes how to deal with the problems and risks that medical artificial intelligence may bring and how to ensure its development in a safe and controllable way based on the growing trend and usage of medical artificial intelligence in China.</t>
+  </si>
+  <si>
+    <t>Statistical Algorithm model of College English Teaching based on artificial Intelligence Technology</t>
+  </si>
+  <si>
+    <t>This paper mainly introduces the principle, characteristics and practical application of artificial intelligence technology in college English teaching system. The system analysis platform of college English teaching is established by using artificial intelligence technology. The platform system is mainly divided into two parts. The first is the expert system model of teacher English assisted instruction based on expert system theory, which is combined with the generation and framework of data analysis. Artificial intelligence has been widely used in college English teaching. Artificial intelligence technology has the advantages of intelligence, data, networking, multimedia and so on. And teaching information collected through artificial intelligence technology mining at the same time, the data using statistical algorithms accurately grasp the students' learning status, to improve and enhance English software platform operation function, improve the operation speed, efficiently for statistical analysis of students' learning behavior, effectively will artificial intelligence technology and system construction depth fusion, promoting the development of digital college English teaching.</t>
+  </si>
+  <si>
+    <t>Research on Coupling Coordination Degree of Artificial Intelligence and Human Capital Investment</t>
+  </si>
+  <si>
+    <t>Artificial intelligence is the leading and representative technology for the development of the digital economy. It is required to realize the self-reliance of high-level science and technology in China and the future's main battlefield of science and technology. Studying the coordination degree of artificial intelligence and human capital investment can understand the coupling and coordination relationship between them and provide direction for policy-making in the future. By constructing a comprehensive index and price system and using the coupling coordination degree model, this paper analyzes the coordinated development degree of artificial intelligence and human capital investment in China in recent 20 years. From the results, there is a positive interaction between artificial intelligence and human capital investment.</t>
+  </si>
+  <si>
+    <t>Systematic Literature Review on Application of Artificial Intelligence in Cancer Detection Using Image Processing</t>
+  </si>
+  <si>
+    <t>Having a low survival rate, cancer has become one of the deadliest diseases with complicated prognosis. In this matter, Artificial Intelligence (AI) is frequently used to aid humans due to the difficulties of cancer identification. Specifically, the use of AI in cancer detection and treatment uses two of its subclasses, machine learning and deep learning. Because those two subclasses can handle large amounts of data, their algorithms can support humans in making decisions that yield the best possible results with the least amount of risk. The purpose of this research is to find out the effectiveness of the Artificial Intelligence algorithm that is used in image processing to diagnose cancer and what is the most effective image processing algorithm for cancer diagnosis. The methods that are used in this research is Systematic Literature Review (SLR). As a result, Artificial Intelligence algorithms are sufficiently effective to be used in diagnosing cancer with image processing. Meanwhile, the most effective algorithm is CatBoost with AUC of 0.939 and Support Vector Machine (SVM) with AUC of 0.934.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence as a facilitator for Film Production Process</t>
+  </si>
+  <si>
+    <t>The development of artificial intelligence (AI) has made it an increasingly important part of film production. The use of AI associated with ML has the potential to completely revolutionise the filmmaking process. The purpose of this research is to examine and synthesise the present state of AI in film production. From pre-production until the film's release, AI has been helpful to the production crew at every stage. This study provides a concise overview of the many stages of the filmmaking process—from pre-production, and post-production to broadcasting—where AI has been widely implemented. We also conducted a survey, using a questionnaire to gauge current and future interest in AI's role in the filmmaking process. The findings demonstrate that using AI in the film industry can enhance the calibre of production and guarantee more earnings at the box office.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence Legal Consulting Based on Categorization</t>
+  </si>
+  <si>
+    <t>With the rapid development of artificial intelligence (AI), it has gradually integrated into people’s lives, and uses its own advantages to help people do things that cannot be done. It seems that AI will continue to develop more comprehensively in the future with more functions and technologies to help people and take some occupations.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence-Driven Protein Folding System Employing Alpha Fold</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence (AI) is a main role to solve the lot of real-live issues. One of the significant challenges in the bioinformatics that researchers have been identified recently is understand the protein folding. First of all, people want to give a big hand off to the advancements because, day to day activities is performed in 3-dimensional basis that is formed based on a sequence of amino acids using protein folds. The folding of proteins is mostly related to three major issues. The first issue is the lack of a specific folding code. There is a folding mechanism in the second one. The ability to ascertain the 3-dimensional structure of proteins presents the last challenge. The structural components and microscopic machinery that make up human cells are called proteins. They provide vital tasks include storing oxygen, breaking down food, and creating scaffolding to support cells in maintaining their structure. Here, Amino acids is formed based on a single chain mechanism because amino acids folds safely and it performs a unique structure that is incorporated here. All living things, including viruses, are composed of proteins, including every element of human body and every other organism. The computational approach can be used to predict the structure of minuscule proteins. In this research work explained about how artificial intelligence is incorporated in predictions of protein structure and artificial intelligence give the solution for the problem of problem folding.</t>
+  </si>
+  <si>
+    <t>AIR5: Five Pillars of Artificial Intelligence Research</t>
+  </si>
+  <si>
+    <t>In this paper, we provide an overview of what we consider to be some of the most pressing research questions currently facing the fields of artificial and computational intelligence (AI and CI). While AI spans a range of methods that enable machines to learn from data and operate autonomously, CI serves as a means to this end by finding its niche in algorithms that are inspired by complex natural phenomena (including the working of the brain). In this paper, we demarcate the key issues surrounding these fields using five unique Rs, namely, rationalizability, resilience, reproducibility, realism, and responsibility. Notably, just as air serves as the basic element of biological life, the term AIR5-cumulatively referring to the five aforementioned Rs-is introduced herein to mark some of the basic elements of artificial life, for sustainable AI and CI. A brief summary of each of the Rs is presented, highlighting their relevance as pillars of future research in this arena.</t>
+  </si>
+  <si>
+    <t>Research on the application of artificial intelligence in computer network technology based on the era of big data</t>
+  </si>
+  <si>
+    <t>With the arrival of the era of big data, the value of artificial intelligence technology has become more and more prominent, and its application in computer network technology has become more extensive. In practice, the application of artificial intelligence in computer network technology can greatly improve the level of security protection of computer networks, and can improve the level of network management, and can better play the advantages of computer network technology. In this regard, this paper firstly introduces big data and artificial intelligence, and analyses the necessity of applying artificial intelligence in computer network technology, and on this basis proposes the specific application of artificial intelligence in computer network technology.</t>
+  </si>
+  <si>
+    <t>Review of Artificial Intelligence Application in Cardiology</t>
+  </si>
+  <si>
+    <t>Increasing incidence of cardiovascular disease and their mortality rate render them as second leading cause of death worldwide. Artificial Intelligence (AI) is used in many fields of science and industry, but also has found its use in medicine for diagnosis, treatment and prediction of diseases. This paper presents the review of AI application in cardiology. The review is based on research papers published in Medline database. Findings of the review indicate that, according to accuracy parameter, the overall performance of AI based models for cardiovascular application is above 83%. Based on the results, AI algorithms and deep learning can be rendered as accurate, hence showing possibility to be used as a diagnostic tool now and in the future. New era of modern diagnosing is coming and Artificial Intelligence has the potential to change the way in which medicine is practiced.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence and Applications</t>
+  </si>
+  <si>
+    <t>Artificial intelligence (AI) has been employed since the 1950s in a number of industries, including manufacturing, logistics, finance, and healthcare. AI is being utilised more and more to automate operations that formerly required human intervention as a result of recent developments in machine learning (ML). AI can be used to automate decision-making procedures and increase the precision of predictions and recommendations. AI can, for instance, be used to determine which people are most likely to contract specific diseases, to suggest the best treatments for those diseases, and to automate the process of approving or rejecting insurance claims, in short healthcare. AI can also be used to identify product flaws and then automatically fix them, enhancing the effectiveness of manufacturing operations. AI can be applied to logistics to improve delivery routes and forecast demand for certain products. AI has a wide range of possible uses, and the opportunities are limitless. AI will probably grow more pervasive in our lives as machine learning continues to progress, altering the way we work, play, and live. In this paper, we will elaborate on the application of artificial intelligence in daily life, such as education, e-shopping, navigation, etc. AI has open vast number of opportunities and increased human efficiency. This has been studied through an intensive literature review concerning matters and applications of AI.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence in Healthcare Supply Chain Management: A Bibliometric Analysis: Subtitle as needed (AI in Healthcare Supply Chain)</t>
+  </si>
+  <si>
+    <t>The presented paper discussed the review of Healthcare Supply Chain Management (HSCM) using Artificial Intelligence (AI). The implementation of artificial intelligence (AI) in HSCM has numerous benefits, including accurate demand forecasting of medical supplies, cost reduction, increased transparency, visibility, data-driven decision-making, enhanced supply chain resilience, streamlined healthcare operations, optimized transportation, and many more. Our approach to using AI in HSCM involved a thorough examination of the literature and bibliometric analysis. Research was started by exploring the Scopus database using suitable keywords. After the inclusion and exclusion criteria have been applied, the relevant papers were gone through full-text readings. Using Vos-viewer, the research papers were further analyzed for bibliometric analysis.</t>
+  </si>
+  <si>
+    <t>The Function of Artificial Intelligence in Business Continuity Management</t>
+  </si>
+  <si>
+    <t>Artificial intelligence (AI) has become a potent instrument in recent years for improving risk evaluation and mitigation strategies in business continuity management (BCM). Therefore, it is important to study the role of various AI technologies, including AI-driven predictive maintenance (AIDPM), AI-powered incident response planning (AIIRP), Natural Language Processing (NLP), and AI-driven data analytics (AIDDA), in improving risk evaluation for business continuity management. This study, specifically focusing on Sao Tome and Principe, where data was collected from a sample of 162 AI specialists across different sectors in country. The findings demonstrate that AI technologies significantly improve the AIDDA and AIDPM on business continuity management. Notably, it was observed that a significant portion of the respondents preferred the outcomes of NLP over manual analysis when it came to risk evaluation. AIIRP integration has greatly decreased business interruptions and accelerated recovery from unforeseen events. The results suggest that while AI can offer substantial benefits in BCM, its effectiveness depends on local conditions and the integration of traditional risk management practices. This case study offers valuable insights for organizations looking to apply artificial intelligence to risk management frameworks, especially in regions facing similar constraints.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence in the Judiciary System of Saudi Arabia: A Literature Review</t>
+  </si>
+  <si>
+    <t>Artificial intelligence (AI) is one of the prominent technological developments in the 21st century. It has gained application in diverse fields, including healthcare, agriculture, and manufacturing. Like other global countries, Saudi Arabia has accelerated its efforts to develop AI. This study aims to investigate AI techniques’ influence on the Saudi judiciary system and determine possible future developments. The study was a literature review of 10 different international and Saudi Arabia publications on Artificial Intelligence in the Judiciary System using related titles, terms, and abstracts. The findings revealed that AI techniques are promising developments in the judiciary. Research evidence supports that augmenting human expertise with appropriate AI techniques like machine learning, text mining, NLP, and machine interpretation can improve efficiency, effectiveness, accuracy, transparency, and fairness in judicial processes. However, the studies focusing on AI applications in the Saudi judicial system are also limited. Despite the limited research, with inferences from the findings from studies in other contexts. AI is a promising development that can improve the Saudi judiciary system. Although these findings provide insight, they are inferential and not an accurate explanation of the influence of AI on the Saudi judicial system. Such gaps call for future studies to determine the influence of AI on the judicial system within the Saudi context.</t>
+  </si>
+  <si>
+    <t>Using Artificial Intelligence Tools in Advertising Product Development</t>
+  </si>
+  <si>
+    <t>Digital technologies and tools are becoming increasingly embedded in all areas of life in today's digital society. The field of advertising is no exception, with innovative resources, in particular artificial intelligence, being actively integrated to create personalised and effective communication campaigns. In the framework of this study, the authors have analysed and systematised the theoretical background and practical solutions for the development of advertising products using artificial intelligence technologies.</t>
+  </si>
+  <si>
+    <t>The Role of Artificial Intelligence in Political Analysis and Decision Aid: “Chat GPT Application” as a Model</t>
+  </si>
+  <si>
+    <t>Political institutions and organizations face many challenges such as information chaos, fake news, and misinformation in light of the spread of technology. There are doubts and concerns about the effectiveness of the use of artificial intelligence by specialists, employees, and academics such as the Chat GPT application in political analysis and its impact on the quality of their information assessment and appropriate decision-making regarding political issues and topics. Hence, the study problem stems from a main question: “What is the role of artificial intelligence such as the Chat GPT application in developing the ability for political analysis and critical thinking and its impact on building the skill of evaluating information and making appropriate decisions regarding political issues and topics?”</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence of Digital Production Management</t>
+  </si>
+  <si>
+    <t>The article considers the application of artificial intelligence (AI) in digital production management. The authors note that the use of AI technologies opens up many opportunities to improve efficiency, optimise processes and make more informed management decisions. Key applications of AI in this area include demand forecasting and production planning, logistics and supply chain optimisation, predictive maintenance of equipment, automation of routine tasks, and big data analysis to uncover hidden patterns. The use of AI in business process management in digital manufacturing, including production process optimisation, supply chain management, quality control, and decision support, is discussed separately. It is emphasised that a key advantage of AI is its ability to process large amounts of data, identify hidden relationships and offer optimal solutions. The article considers the representation of process architecture in digital manufacturing as analogous to neural networks in artificial intelligence. The author notes that this approach has both advantages and disadvantages.</t>
+  </si>
+  <si>
+    <t>An Impact of Artificial Intelligence in Fintech</t>
+  </si>
+  <si>
+    <t>Technological advancements in the last decade have greatly impacted the financial technology (fintech) industry by making financial services more accessible, efficient, and personalized. Out of all these innovations, artificial intelligence (AI) is having the most impact on how the industry is changing. AI is truly a game-changer for the financial sector. It can handle massive volumes of data, spot trends, and make choices with little to no human input. This article examines the function of artificial intelligence (AI) within the financial technology industry, outlining its uses in areas such as algorithmic trading, customer service, credit scoring, lending, investment management, and fraud prevention. It outlines the advantages of AI, which include better risk management, enhanced decision-making, a more satisfying customer experience, and reduced costs and increased efficiency. Data privacy and security, ethical issues, keeping up with regulations, and technical and operational dangers are just few of the issues covered in the article as they pertain to the integration of AI. To demonstrate the revolutionary effect of AI, the article presents case studies of prominent AI deployments in fintech firms. The report concludes by looking ahead to what's to come, speculating that new AI technologies will keep pushing the financial technology industry to innovate. Future financial services will be shaped in new ways by the constant evolution and integration of AI into fintech.</t>
+  </si>
+  <si>
+    <t>Integrating Artificial Intelligence in Management: Opportunities and Ethical Considerations</t>
+  </si>
+  <si>
+    <t>The significance of ethical considerations has been emphasised by management academics and professionals. Nevertheless, there hasn't been much work done till date to theoretically comprehend people's or organisations' ethical stances with regard to Human Resource Management (HRM) decision-making procedures, the choice of particular ethical stances and tactics, or the post-decision accounting for those choices. In order to achieve this, we offer a framework for a throughput model that characterizes people's decision-making in the context of algorithmic HRM. The model illustrates how perceptions, assessments, and information utilisation influence the choice of strategy, showing how the application of specific ethical decision-making algorithmic pathways may enable a variety of tactics. This study sheds light on the various issues regarding the effects and acceptability of integrating artificial intelligence (AI) with human resource management. This research uses multidisciplinary theoretical lenses, including AI-augmented HRM assimilation processes, AI-mediated social exchange, and the judgement and choice literature, to address issues regarding the impact and acceptance of artificial intelligence (AI) integration with HRM. It is suggested that they are of crucial significance in HRM strategy selection and drawing attention to the use of algorithmic ethical perspectives in the adoption of AI for improved HRM outcomes as far as accountability and intelligibility of AI-generated HRM decision-making are concerned.</t>
+  </si>
+  <si>
+    <t>Research on the design of children’s picture-looking and speaking system based on artificial intelligence</t>
+  </si>
+  <si>
+    <t>With the increasing number of images, the machine and describes the image content in image text with people’s reading habits has become an important research content in the field of artificial intelligence. The research goal of this paper is to design and realize a picture speaking system using image text description technology, to apply artificial intelligence technology in the field of education and to assist early childhood education. To achieve this goal, this paper studies the image text description technology.</t>
+  </si>
+  <si>
+    <t>Understanding The Scope Of Artificial Intelligence In HR Technology E-Recruitment – A Theoretical Perspective</t>
+  </si>
+  <si>
+    <t>The expansion of information technology has had a major effect on HR strategies and procedures. The successful transfer of human knowledge into organizational knowledge is crucial while moving toward organizations modeled like edifices, and Artificial Intelligence plays a crucial role in this. This is a crucial stage in the process. Artificial intelligence is a growing area of HR technology that has the potential to either completely replace or vastly improve upon the effectiveness of conventional approaches to personnel administration. Companies can benefit from the use of AI in a number of ways, including applicant screening, employee engagement, retention, and advancement opportunities. It can be used to improve the effectiveness of human resource management by being applied to HR policies, methods, and perspectives. The student will examine the rise of AI in the HRM process and its possible benefits using secondary sources of information. This research provides fresh insights into how technological innovation has helped HRM progress from efficient to long-term viable.</t>
+  </si>
+  <si>
+    <t>Impact Analysis of the Use of Artificial Intelligence with Self-Regulated Learning Theory on Student Academic Performance in Indonesia</t>
+  </si>
+  <si>
+    <t>This study examines the influence of artificial intelligence (AI) on the academic achievement of students in Indonesia, using the self-regulated learning ) theory as a framework. We conducted a study using an online questionnaire that was completed by 242 students. Our analysis focused on the impact of metacognition, motivation, and behavior on academic outcomes. The findings indicate that metacognition accounts for 27.6% of the variation in academic performance, motivation accounts for 44.3%, and behavior contributes to 29.8%. Together, these factors explain a total of 90.7% of the achievement. The results emphasize the importance of educators and parents overseeing the use of AI, ensuring that it improves learning without promoting dependency. The article offers practical suggestions for stakeholders to efficiently utilize artificial intelligence in educational settings, with the goal of enhancing student motivation and academic achievement.</t>
+  </si>
+  <si>
+    <t>Application of artificial intelligence technology in the process of individualized training of air traffic controllers</t>
+  </si>
+  <si>
+    <t>This article is based on a combination of two approaches to improving the professional training of air traffic control controllers: firstly, the individualization of training processes of aviation specialists through the usage of personalized tools for imparting knowledge, taking into account the personal cognitive characteristics of the listener regarding the acquisition and assimilation of educational materials. And secondly, the implementation of professional training of air traffic controllers with help of artificial intelligence technology, which has input markers in the training process, will allow selecting the necessary educational material for the trainee and the instructor in accordance with the individual cognitive and personal abilities of the trainee. Combination of these two approaches allows the training system to carry out the design of a personalized training profile in the maximized degree, oriented to the peculiarities of the student's type of training. Applying of an artificial intelligence discover a huge opportunities in the field of air traffic controllers training for the account of optimization of time and material resources of the training system.</t>
+  </si>
+  <si>
+    <t>Determining the Impact of Artificial Intelligence on Modernization of Education</t>
+  </si>
+  <si>
+    <t>In the process of performing new activities daily, artificial intelligence and new technology are performing new functions. The growth of technology has transformed the working and learning environment, affecting a great number of other systems as well. Most of the other systems that are functioning because of technological advancement have also implemented changes to the learning management systems that assist students in acquiring information via the use of apps that expand their technological experience. Currently, a great number of technology applications are working with machine learning and offering new ways of learning for students. These new learning methods may simplify the acquisition of the developing material for students. The purpose of this research was to determine the factors that influence the level of motivation and efficiency among students attending higher education institutions. This study found that most learners have shown a positive response to the applications of artificial intelligence. The positive response can be attributed to the following factors: learning applications help with learning the content, enhance the learning capabilities of learners, and produce confidence in the development of core ideas about the learning content. The findings of this research revealed that if training and curriculum sessions will be implemented in higher education institutions, then learners would have a favorable rise in their motivation towards applications, and they would also develop an interest in the process of learning overall.</t>
+  </si>
+  <si>
+    <t>Analysis the Impact of Artificial Intelligence on College Student Employment Based on Data Mining</t>
+  </si>
+  <si>
+    <t>With the continuous development of artificial intelligence(AI), its influence is becoming more and more extensive. The development of AI and the employment of college students are both hot topics in today's society. In order to analyze the situation of college students using AI technology and the impact of AI on the employment of college students. We crawled 2398 job recruitment information from the website and conducted a questionnaire survey of college students. Identifying the relatively popular professional fields under the context of AI, and binary logistic regression was used to model the factors affecting students' use of artificial intelligence technology. The research results provide a good reference for students' career planning.</t>
+  </si>
+  <si>
+    <t>A Review of Strategies for the Application of Artificial Intelligence Technologies in the Operation of Grid Enterprises</t>
+  </si>
+  <si>
+    <t>With the rapid development of Artificial Intelligence (AI) technology, the power grid industry is gradually increasing its investment in a new generation of information technology in the digital and intelligent transformation, and is committed to creating a full-process digital intelligence system to improve the operational efficiency and reliability of the power system. The purpose of this paper is to comprehensively explore the application strategy of AI in various aspects of power grid operation and its practical effects, to make a comprehensive and systematic compendium of it, and to construct a complete application framework. It also provides an in-depth analysis of the challenges faced by AI technology in the operation process as well as the countermeasures to provide reference for other power-related enterprises.</t>
+  </si>
+  <si>
+    <t>Innovative Approaches in Artificial Intelligence: Current Trends Shaping the Technological Future</t>
+  </si>
+  <si>
+    <t>This paper provides an in-depth analysis of current trends in artificial intelligence, with a focus on developments from 2022 to the present. The aim is to identify and examine the key areas that are currently shaping the direction of this rapidly evolving field. Our analysis is based on an extensive study of specialized books, publications, and other relevant sources released during this period. We focus on advancements in machine learning, breakthrough technologies, ethical issues related to AI implementation, as well as new applications and their impact across various sectors, such as healthcare, finance, and industry. The paper offers a comprehensive overview of current trends and discusses their potential implications for the future of technology, the economy, and society as a whole.</t>
+  </si>
+  <si>
+    <t>Research on the Development path of Logistics and Express Delivery Industry in the Era of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>With the development of artificial intelligence technology, the logistics and express delivery industry is undergoing profound changes. In order to adapt to the increasingly fierce competition, Big data analysis and Cloud-based artificial intelligence technology are widely adopted in the logistics and express delivery industry. The future has coming, the express delivery industry is undergoing a new round of reshuffle. The intelligent technology has saved the human cost, and at the same time has gradually raised the threshold of the express delivery industry, making it more and more technology-intensive. Then how will the future logistics and express industry develop? What are the development paths in the context of artificial intelligence? This paper will discuss the development of logistics and express delivery industry under artificial intelligence based on the current development status.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence Impact on Administrative Decision-Making at Zain Bahrain Telecommunication Company</t>
+  </si>
+  <si>
+    <t>This research aims to identify the impact of artificial intelligence on administrative decision-making (flexibility, value &amp; integration) at Zain Bahrain Telecommunication Company. Four hundred and three employees were surveyed through a simple random sampling method. The analysis is based on the outcomes of the questionnaire survey that was given out to a representative sample of the employees at the company in question. Researchers hypothesized that there is a positive significant impact of artificial intelligence on administrative decision-making (flexibility, value &amp; integration) at Zain Bahrain Telecommunication Company. The findings indicated that this hypothesis was accepted. Moreover, the results indicated that there are no significant differences relating to the impact of artificial intelligence on administrative decision-making (flexibility, value &amp; integration) at Zain Bahrain Telecommunication Company due to the demographic (age, qualification, and years of experience). At the same time, there are differences due to (gender and position).</t>
+  </si>
+  <si>
+    <t>Challenges to Ensuring Information Security and the Role of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>This paper examines the integration of Artificial Intelligence (AI) in addressing contemporary cybersecurity challenges. The digital age's expanding data landscape and evolving cyber threats have rendered traditional security measures inadequate. AI emerges as a critical tool, capable of analyzing vast datasets, detecting anomalies, and adapting to new threats in real-time. The study explores the history and evolution of AI, focusing on its applications in intrusion detection, malware analysis, and predictive analytics. Challenges such as adversarial exploitation, algorithmic biases, and implementation complexities are also discussed. Future prospects emphasize enhancing AI accuracy, transparency, and collaboration with emerging technologies like IoT and quantum computing. The findings underscore AI's transformative potential in cybersecurity while highlighting the need for ethical and robust implementation.</t>
+  </si>
+  <si>
+    <t>Revolutionizing Healthcare: The Impact of Artificial Intelligence on Precision Diagnoses and Patient Outcomes</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence (AI) has reached a level of precision comparable to human expertise in the medical field, utilizing sophisticated algorithms for intricate imaging calculations that identify abnormalities and enhance clinical outcomes. The integration of AI in healthcare is transforming the ideal system by improving diagnostic accuracy, particularly in low-income countries where AI-driven robots hold promise for addressing global health challenges. This convergence of machine capabilities is revolutionizing healthcare culture, with AI modules focused on image acquisition and machine learning playing a pivotal role in advancing practices. These technologies not only facilitate public access to digital consultations through wearable's but also provide a practical alternative to frequent hospital visits. Recent research emphasizes the promising potential of AI modules in addressing mental disorders, diagnosing respiratory diseases, and early identification of chronic and potentially fatal conditions such as cancer. The rapid expansion of AI modules is not only increasing survival rates but is also significantly enhancing the overall quality of treatment.</t>
+  </si>
+  <si>
+    <t>The application of cognitive artificial intelligence within C4ISR framework for national resilience</t>
+  </si>
+  <si>
+    <t>Cognitive Artificial Intelligence (CAI) is a new perspective in Artificial Intelligence (AI) which is aimed to emulate how human brain works in generating knowledge. Human becomes intelligent because of knowledge which grows over time in his brain. With comprehensive knowledge, he can understand the world (environment) and is able to make decision and or action on it. On the other hand, strategic decision which impacts to the continuance of having a nation and having state is a critical and crucial matter, and it should be done in precise and quick manner especially in the case of contingency and faced to mutiple-data multiple-decision-alternative problems. The most precise decision has to be based on the knowledge from extracted comprehensive information. In this paper we show you the application of CAI for National Security with Knowledge-Growing System (KGS) as the engine of decision making system. We apply the CAI to a framework called Cognitive Command, Control, Communications, Computers, Intelligence, Surveillance and Reconnaissance (C4ISR) with examples taken from a simulated of real-life case in the Defense-Security domain.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence in OSCE: Innovations and Implications for Medical Education Assessment – A Systematic Review</t>
+  </si>
+  <si>
+    <t>Objective Structured Clinical Examinations (OSCEs) are cornerstone for evaluation of competencies pertaining to clinical medicine. The recent advent of artificial intelligence has given rise to newer opportunities which evidently have improved the reliability, validity, objectivity of OSCE. This draft deals into the concept of integration of artificial intelligence into OSCE with proper focus on technology technology innovations there in such as provision of real-time feedback and incorporation of virtual simulations as well. As per the PRISMA guidelines, we conducted a literature search and analysed studies available in literature from 2018 till 2024. We have concluded that artificial intelligence as a technological innovation in the world of assessment of clinical competencies. In medical education has a very strong potential to reduce examiner bias, provision of detailed feedback, and simulating realistic clinical scenarios. Still, certain challenges and limitation such as lack of emotional intelligence and the human touch to the entire assessment. Scenario seems to be lagging and is therefore much needed to retain the learning curve of the modern day learners.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence applications addressing different aspects of the Covid-19 crisis and key technological solutions for future epidemics control</t>
+  </si>
+  <si>
+    <t>Artificial intelligence (AI) development and its application in human life are continuing at an astounding rate. Among the variety of examples of AI being used for a variety of tasks, its contribution to epidemic control has recently captured a great deal of interest at the time of the recent Covid-19 pandemic, a crisis that occurred due to the Coronavirus spread. As the entire world has been concerning over urgent efforts addressing the damaging effects since the outbreak, Artificial Intelligence emerged as a great possible solution. This study is aimed at examining how artificial intelligence gets us ready to combat and control COVID-19 and other future pandemics, as this is unlikely to be the last of the epidemics. Moreover, several key technological solutions are outlined that could help combat future pandemics and make us prepared. As a result, technology development can be promoted to overcome any possible unexpected subsequent crisis.</t>
+  </si>
+  <si>
+    <t>Artificial intelligence neural networks: Split personality</t>
+  </si>
+  <si>
+    <t>THE FIRST meeting on artificial intelligence did not go all that well. In summer 1956, on the back of early successes in computer design, leading lights of the new science of information theory met at Dartmouth College in New Hampshire to thrash out a plan for emulating the thought processes of the human mind. The organisers thought it would just take a summer school to formulate a coherent programme of research to ultimately create a human-level intelligence.</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence: Investigating the Impact of Teacher’s Awareness, Perception, and Learning Motivation on Learning Evaluation</t>
+  </si>
+  <si>
+    <t>Artificial intelligence (AI) is a reality for teachers in today’s rapidly evolving technological landscape. AI’s application in education has the potential to improve classroom learning efficiency. However, many teachers in Indonesia still don’t have any awareness of artificial intelligence. Teachers’ perspectives on AI are limited to technologies used outside of education, so motivation to learn about AI must be strengthened. Teachers’ lack of understanding of these influences how they evaluate student learning in the classroom. With the world’s fourth-largest internet user base, Indonesia is considered a technologically literate country. As a result, the purpose of this research is to learn more about AI and its applications in Indonesian education. This study also seeks to determine the extent to which instructor understanding, perception, and motivation to learn about artificial intelligence (AI) influence classroom learning evaluation. This study included 502 Indonesian teachers from kindergarten to high school who had at least a bachelor’s or master’s degree. The SPSS 21 program validated and analysed the instruments used in this study. We performed statistical tests on the data to establish a relationship between the independent and dependent variables. This study used a simultaneous one-way ANOVA test to establish the size of the influence between factors. This study revealed several facts about the use of AI in Indonesian education, showing that teacher awareness, perception, and motivation to learn about AI all impact the evaluation of learning.</t>
+  </si>
+  <si>
+    <t>Automatic Acquisition Method of Geotechnical Engineering Survey Data based on Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>The process of collecting survey data, the traditional automatic acquisition method of geotechnical engineering survey data does not integrate enough information, resulting in high packet loss rate. Therefore, an automatic data acquisition method for geotechnical engineering survey based on artificial intelligence is proposed. The 3D laser scanning data can be obtained to represent the local characteristics of rock and soil. GPS control network is set up to collect d-level and e-level GPS data. The information state features are extracted by using artificial agent, and the above data are integrated to realize the automatic acquisition of survey data. Comparing this method with the two traditional methods to collect cross-section node information of rock-soil tunnels, the results show that this method reduces the data packet loss rate and ensures the integrity of survey data.</t>
+  </si>
+  <si>
+    <t>The Importance of Artificial Intelligence in Green Innovation</t>
+  </si>
+  <si>
+    <t>The study focuses on Artificial Intelligence’s importance in developing green innovation. Artificial intelligence significantly enhances green innovation by enhancing productivity, accelerating environmentally friendly technological advancements, and facilitating better decision-making through energy optimisation, waste reduction, and smart infrastructure support. This research adopted a scoping review approach utilising the Scopus database as a source of documents. The study highlights several aspects, such as publication trend by years, publication source and context analysis. The reviews included documents published since 2021. The method section is derived from the PRISM-ScR checklist table. The highest publisher was the Business Strategy and The Environment journal, and the country with the highest publishing was China. In addition, the study recommends that more efforts should be exerted to increase companies’ awareness of the importance of green innovation and the feasibility of developing green products.</t>
+  </si>
+  <si>
+    <t>Overview on Quantum Computing and its Applications in Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>This paper will review the basic building blocks of quantum computing and discuss the main applications in artificial intelligence that can be addressed more efficiently using the quantum computers of today. Artificial intelligence and quantum computing have many features in common. Quantum computing can provide artificial intelligence and machine learning algorithms with speed of training and computational power in less price. Artificial intelligence on the other hand can provide quantum computers with the necessary error correction algorithms. Some of the algorithms in AI that have been successfully implemented on a quantum computer, that we will present in this paper, are both unsupervised learning algorithms (clustering and Principal component analysis) and also supervised learning classification, such as support vector machines.</t>
+  </si>
+  <si>
+    <t>Revolutionizing Transportation System Using Artificial Intelligence Technique</t>
+  </si>
+  <si>
+    <t>The development of artificial intelligence (AI) in a variety of fields, particularly in autonomous vehicles and traffic control. It emphasizes the historical backdrop while highlighting AI's aim to mimic human cognitive powers. Discusses the problem of drowsy driving and looks into detecting methods. In-depth discussions of traffic control problems are also covered, along with cutting-edge solutions such as Convolutional Neural Network (CNN) models for detecting pre-drowsiness and inexpensive smartphone technology for road monitoring. These developments demonstrate AI has the power to alter the way that traffic and road safety are managed internationally. In this paper discuss about use of Artificial Intelligence (AI) to solve problems in manufacturing, safety, and public transportation in the transportation sector. It talks about AI solutions for sleepiness detection, road monitoring, and autonomous driving. The application of AI promises to revolutionize the industry globally with safer roads, quicker travel, and inventive unmanned technologies.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1819,14 +2702,46 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2E3743"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1848,19 +2763,25 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2177,15 +3098,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20623948-7910-4CC3-B037-54C71365A541}">
   <dimension ref="A1:H1048478"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.109375" customWidth="1"/>
-    <col min="3" max="3" width="20.77734375" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="2" width="23.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="39.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2205,3117 +3128,5118 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F2" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="F2" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F3" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="F3" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="F4" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="F5" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F6" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="F6" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F7" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="F7" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F8" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="F8" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F9" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="F9" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F10" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="F10" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F11" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="F11" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F12" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="F12" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F14" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="F14" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F15" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="F15" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F16" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="F16" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F17" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="F17" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F18" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="F18" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F19" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="F19" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F20" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="F20" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F21" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="F21" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F22" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="F22" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F23" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="F23" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F24" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="F24" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F25" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26">
+      <c r="F25" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F26" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27">
+      <c r="F26" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F27" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28">
+      <c r="F27" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F28" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29">
+      <c r="F28" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="F29" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30">
+      <c r="F29" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="F30" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31">
+      <c r="F30" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="F31" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="F31" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="F32" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="F32" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F33" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="F33" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F34" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="F34" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F35" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="F35" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="F36" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37">
+      <c r="F36" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="F37" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="F37" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F38" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="F38" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F39" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40">
+      <c r="F39" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="F40" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41">
+      <c r="F40" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F41" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42">
+      <c r="F41" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="F42" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43">
+      <c r="F42" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F43" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44">
+      <c r="F43" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="F44" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45">
+      <c r="F44" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="F45" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46">
+      <c r="F45" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="F46" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47">
+      <c r="F46" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
         <v>46</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="F47" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48">
+      <c r="F47" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B48" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="F48" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49">
+      <c r="F48" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
         <v>48</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="F49" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50">
+      <c r="F49" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
         <v>49</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="F50" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51">
+      <c r="F50" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
         <v>50</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="F51" t="s">
-        <v>407</v>
-      </c>
-      <c r="H51" s="3" t="s">
+      <c r="F51" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="H51" s="4" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
         <v>51</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D52" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="F52" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53">
+      <c r="F52" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
         <v>52</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D53" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="F53" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54">
+      <c r="F53" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D54" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="F54" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55">
+      <c r="F54" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
         <v>54</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D55" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="F55" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56">
+      <c r="F55" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="F56" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57">
+      <c r="F56" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="3">
         <v>56</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D57" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="F57" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58">
+      <c r="F57" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="3">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D58" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E58" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F58" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59">
+      <c r="F58" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="3">
         <v>58</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D59" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="F59" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60">
+      <c r="F59" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="3">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D60" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="F60" t="s">
-        <v>407</v>
-      </c>
-      <c r="G60" s="3"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61">
+      <c r="F60" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="G60" s="4"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
         <v>60</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D61" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="E61" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="F61" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62">
+      <c r="F61" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E62" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="F62" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63">
+      <c r="F62" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
         <v>62</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D63" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="F63" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64">
+      <c r="F63" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D64" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="F64" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65">
+      <c r="F64" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="F65" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66">
+      <c r="F65" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D66" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E66" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="F66" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67">
+      <c r="F66" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D67" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="F67" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68">
+      <c r="F67" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D68" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="F68" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69">
+      <c r="F68" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
         <v>68</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D69" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E69" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="F69" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70">
+      <c r="F69" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D70" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="F70" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71">
+      <c r="F70" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D71" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="F71" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72">
+      <c r="F71" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D72" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E72" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="F72" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73">
+      <c r="F72" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
         <v>72</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E73" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="F73" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74">
+      <c r="F73" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D74" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="E74" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="F74" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75">
+      <c r="F74" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
         <v>74</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D75" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E75" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="F75" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76">
+      <c r="F75" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="E76" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="F76" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77">
+      <c r="F76" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
         <v>76</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D77" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E77" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="F77" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78">
+      <c r="F77" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D78" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E78" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="F78" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79">
+      <c r="F78" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
         <v>78</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D79" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="F79" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80">
+      <c r="F79" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="F80" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81">
+      <c r="F80" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
         <v>80</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="F81" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82">
+      <c r="F81" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E82" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="F82" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83">
+      <c r="F82" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
         <v>82</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E83" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="F83" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84">
+      <c r="F83" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="3">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E84" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="F84" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85">
+      <c r="F84" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="3">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E85" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="F85" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86">
+      <c r="F85" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="3">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="E86" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="F86" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87">
+      <c r="F86" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="3">
         <v>86</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E87" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="F87" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88">
+      <c r="F87" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="3">
         <v>87</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E88" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="F88" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89">
+      <c r="F88" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="3">
         <v>88</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="E89" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="F89" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90">
+      <c r="F89" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="3">
         <v>89</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E90" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="F90" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91">
+      <c r="F90" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="3">
         <v>90</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E91" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="F91" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92">
+      <c r="F91" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="3">
         <v>91</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="E92" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="F92" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93">
+      <c r="F92" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="3">
         <v>92</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="E93" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="F93" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94">
+      <c r="F93" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="3">
         <v>93</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B94" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="E94" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="F94" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95">
+      <c r="F94" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
         <v>94</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B95" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E95" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="F95" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96">
+      <c r="F95" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
         <v>95</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="E96" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="F96" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97">
+      <c r="F96" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="3">
         <v>96</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B97" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="E97" s="3" t="s">
+      <c r="E97" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="F97" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98">
+      <c r="F97" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="3">
         <v>97</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B98" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="E98" s="3" t="s">
+      <c r="E98" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="F98" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99">
+      <c r="F98" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="3">
         <v>98</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B99" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="E99" s="3" t="s">
+      <c r="E99" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="F99" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100">
+      <c r="F99" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="3">
         <v>99</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="F100" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101">
+      <c r="F100" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="3">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="E101" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="F101" t="s">
-        <v>407</v>
-      </c>
-      <c r="G101" s="3" t="s">
+      <c r="F101" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="G101" s="4" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="3">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E102" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="F102" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103">
+      <c r="F102" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="3">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E103" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="F103" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104">
+      <c r="F103" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="3">
         <v>103</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C104" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D104" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E104" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="F104" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105">
+      <c r="F104" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="3">
         <v>104</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C105" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E105" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="F105" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106">
+      <c r="F105" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="3">
         <v>105</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C106" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D106" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E106" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="F106" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107">
+      <c r="F106" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="3">
         <v>106</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B107" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C107" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D107" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="E107" s="1" t="s">
+      <c r="E107" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="F107" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108">
+      <c r="F107" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="3">
         <v>107</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B108" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C108" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D108" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="E108" s="1" t="s">
+      <c r="E108" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="F108" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109">
+      <c r="F108" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="3">
         <v>108</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B109" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C109" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D109" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="E109" s="1" t="s">
+      <c r="E109" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="F109" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110">
+      <c r="F109" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="3">
         <v>109</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B110" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C110" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D110" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="E110" s="1" t="s">
+      <c r="E110" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="F110" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111">
+      <c r="F110" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="3">
         <v>110</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C111" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D111" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="E111" s="1" t="s">
+      <c r="E111" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="F111" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112">
+      <c r="F111" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="3">
         <v>111</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C112" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D112" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="E112" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="F112" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113">
+      <c r="F112" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="3">
         <v>112</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B113" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C113" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D113" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E113" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="F113" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114">
+      <c r="F113" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="3">
         <v>113</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B114" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C114" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D114" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E114" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="F114" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115">
+      <c r="F114" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="3">
         <v>114</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B115" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C115" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D115" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="E115" s="1" t="s">
+      <c r="E115" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="F115" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116">
+      <c r="F115" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="3">
         <v>115</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B116" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C116" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D116" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E116" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="F116" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117">
+      <c r="F116" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="3">
         <v>116</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C117" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D117" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E117" s="1" t="s">
+      <c r="E117" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="F117" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118">
+      <c r="F117" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="3">
         <v>117</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D118" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E118" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="F118" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119">
+      <c r="F118" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="3">
         <v>118</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C119" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D119" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="E119" s="1" t="s">
+      <c r="E119" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="F119" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120">
+      <c r="F119" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="3">
         <v>119</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C120" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D120" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="E120" s="1" t="s">
+      <c r="E120" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="F120" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121">
+      <c r="F120" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="3">
         <v>120</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C121" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D121" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="E121" s="1" t="s">
+      <c r="E121" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="F121" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122">
+      <c r="F121" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="3">
         <v>121</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C122" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D122" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="E122" s="1" t="s">
+      <c r="E122" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="F122" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123">
+      <c r="F122" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="3">
         <v>122</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C123" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D123" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="E123" s="1" t="s">
+      <c r="E123" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="F123" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124">
+      <c r="F123" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="3">
         <v>123</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C124" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D124" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="E124" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="F124" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125">
+      <c r="F124" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="3">
         <v>124</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C125" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D125" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="E125" s="1" t="s">
+      <c r="E125" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="F125" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126">
+      <c r="F125" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="3">
         <v>125</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C126" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D126" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="E126" s="1" t="s">
+      <c r="E126" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="F126" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127">
+      <c r="F126" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="3">
         <v>126</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C127" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D127" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="E127" s="1" t="s">
+      <c r="E127" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="F127" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128">
+      <c r="F127" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="3">
         <v>127</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C128" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D128" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="E128" s="1" t="s">
+      <c r="E128" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="F128" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129">
+      <c r="F128" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="3">
         <v>128</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C129" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D129" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="E129" s="1" t="s">
+      <c r="E129" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="F129" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130">
+      <c r="F129" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="3">
         <v>129</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C130" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D130" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="E130" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="F130" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131">
+      <c r="F130" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="3">
         <v>130</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C131" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D131" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="E131" s="1" t="s">
+      <c r="E131" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="F131" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132">
+      <c r="F131" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="3">
         <v>131</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C132" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D132" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="E132" s="1" t="s">
+      <c r="E132" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="F132" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133">
+      <c r="F132" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="3">
         <v>132</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C133" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D133" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="E133" s="1" t="s">
+      <c r="E133" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="F133" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134">
+      <c r="F133" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="3">
         <v>133</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C134" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D134" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="E134" s="5" t="s">
         <v>506</v>
       </c>
-      <c r="F134" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135">
+      <c r="F134" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="3">
         <v>134</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C135" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="D135" t="s">
+      <c r="D135" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="E135" s="1" t="s">
+      <c r="E135" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="F135" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136">
+      <c r="F135" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="3">
         <v>135</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C136" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D136" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="E136" s="1" t="s">
+      <c r="E136" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="F136" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137">
+      <c r="F136" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="3">
         <v>136</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B137" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C137" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D137" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="E137" s="1" t="s">
+      <c r="E137" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="F137" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138">
+      <c r="F137" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="3">
         <v>137</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B138" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C138" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D138" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="E138" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="F138" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139">
+      <c r="F138" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="3">
         <v>138</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B139" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D139" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="E139" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="F139" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140">
+      <c r="F139" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="3">
         <v>139</v>
       </c>
-      <c r="B140" t="s">
+      <c r="B140" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="D140" t="s">
+      <c r="D140" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="E140" s="1" t="s">
+      <c r="E140" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="F140" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141">
+      <c r="F140" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="3">
         <v>140</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B141" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C141" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="D141" t="s">
+      <c r="D141" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="E141" s="7" t="s">
+      <c r="E141" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="F141" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142">
+      <c r="F141" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="3">
         <v>141</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B142" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C142" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D142" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="E142" s="1" t="s">
+      <c r="E142" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="F142" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143">
+      <c r="F142" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="3">
         <v>142</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B143" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C143" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D143" t="s">
+      <c r="D143" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="E143" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="F143" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144">
+      <c r="F143" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="3">
         <v>143</v>
       </c>
-      <c r="B144" t="s">
+      <c r="B144" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C144" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="D144" t="s">
+      <c r="D144" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="E144" s="1" t="s">
+      <c r="E144" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="F144" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145">
+      <c r="F144" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="3">
         <v>144</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B145" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C145" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="D145" t="s">
+      <c r="D145" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="E145" s="1" t="s">
+      <c r="E145" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="F145" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146">
+      <c r="F145" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="3">
         <v>145</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B146" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C146" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D146" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="E146" s="1" t="s">
+      <c r="E146" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="F146" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147">
+      <c r="F146" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="3">
         <v>146</v>
       </c>
-      <c r="B147" t="s">
+      <c r="B147" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C147" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="D147" t="s">
+      <c r="D147" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="E147" s="1" t="s">
+      <c r="E147" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="F147" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148">
+      <c r="F147" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="3">
         <v>147</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B148" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C148" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D148" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="E148" s="1" t="s">
+      <c r="E148" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="F148" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149">
+      <c r="F148" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="3">
         <v>148</v>
       </c>
-      <c r="B149" t="s">
+      <c r="B149" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="C149" t="s">
+      <c r="C149" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="D149" t="s">
+      <c r="D149" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="E149" s="1" t="s">
+      <c r="E149" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="F149" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150">
+      <c r="F149" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="3">
         <v>149</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B150" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C150" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="D150" t="s">
+      <c r="D150" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="E150" s="1" t="s">
+      <c r="E150" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="F150" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151">
+      <c r="F150" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="3">
         <v>150</v>
       </c>
-      <c r="B151" t="s">
+      <c r="B151" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C151" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="D151" t="s">
+      <c r="D151" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="E151" s="1" t="s">
+      <c r="E151" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="F151" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152">
+      <c r="F151" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="3">
         <v>151</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153">
+      <c r="B152" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="C152" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="3">
         <v>152</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154">
+      <c r="B153" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="C153" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="3">
         <v>153</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155">
+      <c r="B154" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C154" s="11" t="s">
+        <v>579</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="3">
         <v>154</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156">
+      <c r="B155" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="C155" s="11" t="s">
+        <v>581</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="3">
         <v>155</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157">
+      <c r="B156" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="C156" s="11" t="s">
+        <v>583</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="3">
         <v>156</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158">
+      <c r="B157" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="C157" s="11" t="s">
+        <v>585</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="3">
         <v>157</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159">
+      <c r="B158" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="C158" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="3">
         <v>158</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A160">
+      <c r="B159" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="C159" s="11" t="s">
+        <v>589</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="3">
         <v>159</v>
       </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A161">
+      <c r="B160" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="C160" s="11" t="s">
+        <v>591</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="3">
         <v>160</v>
       </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A162">
+      <c r="B161" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="C161" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="3">
         <v>161</v>
       </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A163">
+      <c r="B162" s="9" t="s">
+        <v>594</v>
+      </c>
+      <c r="C162" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="3">
         <v>162</v>
       </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A164">
+      <c r="B163" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="C163" s="11" t="s">
+        <v>597</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="3">
         <v>163</v>
       </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A165">
+      <c r="B164" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>599</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="3">
         <v>164</v>
       </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A166">
+      <c r="B165" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="C165" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="3">
         <v>165</v>
       </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A167">
+      <c r="B166" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="C166" s="11" t="s">
+        <v>602</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="3">
         <v>166</v>
       </c>
-    </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A168">
+      <c r="B167" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C167" s="10" t="s">
+        <v>604</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="3">
         <v>167</v>
       </c>
-    </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A169">
+      <c r="B168" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="3">
         <v>168</v>
       </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A170">
+      <c r="B169" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C169" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="3">
         <v>169</v>
       </c>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A171">
+      <c r="B170" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="3">
         <v>170</v>
       </c>
-    </row>
-    <row r="1048472" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1048473" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1048474" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1048475" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1048476" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1048477" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="1048478" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="B171" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C171" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="3">
+        <v>171</v>
+      </c>
+      <c r="B172" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="3">
+        <v>172</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="3">
+        <v>173</v>
+      </c>
+      <c r="B174" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="C174" s="10" t="s">
+        <v>618</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="3">
+        <v>174</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="C175" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" s="3">
+        <v>175</v>
+      </c>
+      <c r="B176" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>622</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="3">
+        <v>176</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C177" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="3">
+        <v>177</v>
+      </c>
+      <c r="B178" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="C178" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" s="3">
+        <v>178</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C179" s="10" t="s">
+        <v>628</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="3">
+        <v>179</v>
+      </c>
+      <c r="B180" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="C180" s="10" t="s">
+        <v>630</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="3">
+        <v>180</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="C181" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" s="3">
+        <v>181</v>
+      </c>
+      <c r="B182" s="9" t="s">
+        <v>633</v>
+      </c>
+      <c r="C182" s="10" t="s">
+        <v>634</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="3">
+        <v>182</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="C183" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="3">
+        <v>183</v>
+      </c>
+      <c r="B184" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="C184" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="3">
+        <v>184</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C185" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="3">
+        <v>185</v>
+      </c>
+      <c r="B186" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="C186" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="3">
+        <v>186</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C187" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="3">
+        <v>187</v>
+      </c>
+      <c r="B188" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="3">
+        <v>188</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="C189" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="3">
+        <v>189</v>
+      </c>
+      <c r="B190" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="C190" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="3">
+        <v>190</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C191" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="3">
+        <v>191</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="C192" s="10" t="s">
+        <v>652</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" s="3">
+        <v>192</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C193" s="10" t="s">
+        <v>654</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" s="3">
+        <v>193</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="C194" s="10" t="s">
+        <v>656</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" s="3">
+        <v>194</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" s="3">
+        <v>195</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="C196" s="10" t="s">
+        <v>660</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" s="3">
+        <v>196</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="C197" s="10" t="s">
+        <v>662</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" s="3">
+        <v>197</v>
+      </c>
+      <c r="B198" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" s="3">
+        <v>198</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="C199" s="10" t="s">
+        <v>666</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="3">
+        <v>199</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="C200" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="3">
+        <v>200</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="C201" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="3">
+        <v>201</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="3">
+        <v>202</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" s="3">
+        <v>203</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" s="3">
+        <v>204</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" s="3">
+        <v>205</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="3">
+        <v>206</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" s="3">
+        <v>207</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" s="3">
+        <v>208</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" s="3">
+        <v>209</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" s="3">
+        <v>210</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" s="3">
+        <v>211</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" s="3">
+        <v>212</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" s="3">
+        <v>213</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" s="3">
+        <v>214</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" s="3">
+        <v>215</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" s="3">
+        <v>216</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" s="3">
+        <v>217</v>
+      </c>
+      <c r="B219" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" s="3">
+        <v>218</v>
+      </c>
+      <c r="B220" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" s="3">
+        <v>219</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" s="3">
+        <v>220</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" s="3">
+        <v>221</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" s="3">
+        <v>222</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" s="3">
+        <v>223</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" s="3">
+        <v>224</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" s="3">
+        <v>225</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228" s="3">
+        <v>226</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A229" s="3">
+        <v>227</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" s="3">
+        <v>228</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" s="3">
+        <v>229</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" s="3">
+        <v>230</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" s="3">
+        <v>231</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" s="3">
+        <v>232</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="3">
+        <v>233</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" s="3">
+        <v>234</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" s="3">
+        <v>235</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238" s="3">
+        <v>236</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239" s="3">
+        <v>237</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A240" s="3">
+        <v>238</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A241" s="3">
+        <v>239</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A242" s="3">
+        <v>240</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A243" s="3">
+        <v>241</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A244" s="3">
+        <v>242</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A245" s="3">
+        <v>243</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A246" s="3">
+        <v>244</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A247" s="3">
+        <v>245</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A248" s="3">
+        <v>246</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A249" s="3">
+        <v>247</v>
+      </c>
+      <c r="B249" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A250" s="3">
+        <v>248</v>
+      </c>
+      <c r="B250" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A251" s="3">
+        <v>249</v>
+      </c>
+      <c r="B251" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>768</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A252" s="3">
+        <v>250</v>
+      </c>
+      <c r="B252" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A253" s="3">
+        <v>251</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A254" s="3">
+        <v>252</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A255" s="3">
+        <v>253</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256" s="3">
+        <v>254</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A257" s="3">
+        <v>255</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A258" s="3">
+        <v>256</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A259" s="3">
+        <v>257</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A260" s="3">
+        <v>258</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A261" s="3">
+        <v>259</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A262" s="3">
+        <v>260</v>
+      </c>
+      <c r="B262" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263" s="3">
+        <v>261</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" s="3">
+        <v>262</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A265" s="3">
+        <v>263</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A266" s="3">
+        <v>264</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A267" s="3">
+        <v>265</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A268" s="3">
+        <v>266</v>
+      </c>
+      <c r="B268" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A269" s="3">
+        <v>267</v>
+      </c>
+      <c r="B269" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A270" s="3">
+        <v>268</v>
+      </c>
+      <c r="B270" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A271" s="3">
+        <v>269</v>
+      </c>
+      <c r="B271" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A272" s="3">
+        <v>270</v>
+      </c>
+      <c r="B272" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="F272" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A273" s="3">
+        <v>271</v>
+      </c>
+      <c r="B273" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="F273" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A274" s="3">
+        <v>272</v>
+      </c>
+      <c r="B274" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A275" s="3">
+        <v>273</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A276" s="3">
+        <v>274</v>
+      </c>
+      <c r="B276" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A277" s="3">
+        <v>275</v>
+      </c>
+      <c r="B277" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A278" s="3">
+        <v>276</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="F278" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A279" s="3">
+        <v>277</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A280" s="3">
+        <v>278</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A281" s="3">
+        <v>279</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="F281" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A282" s="3">
+        <v>280</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="F282" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A283" s="3">
+        <v>281</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A284" s="3">
+        <v>282</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="C284" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A285" s="3">
+        <v>283</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="F285" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A286" s="3">
+        <v>284</v>
+      </c>
+      <c r="B286" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="C286" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="F286" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A287" s="3">
+        <v>285</v>
+      </c>
+      <c r="B287" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="F287" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A288" s="3">
+        <v>286</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="C288" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="F288" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A289" s="3">
+        <v>287</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="C289" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="F289" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A290" s="3">
+        <v>288</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="C290" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="F290" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A291" s="3">
+        <v>289</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="C291" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="F291" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A292" s="3">
+        <v>290</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A293" s="3">
+        <v>291</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="C293" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A294" s="3">
+        <v>292</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="C294" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A295" s="3">
+        <v>293</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="C295" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="F295" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A296" s="3">
+        <v>294</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="C296" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="F296" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A297" s="3">
+        <v>295</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="C297" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="F297" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A298" s="3">
+        <v>296</v>
+      </c>
+      <c r="B298" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="C298" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="F298" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A299" s="3">
+        <v>297</v>
+      </c>
+      <c r="B299" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="C299" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A300" s="3">
+        <v>298</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="C300" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="F300" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" s="3">
+        <v>299</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="C301" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="F301" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A302" s="3">
+        <v>300</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="C302" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="1048472" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048473" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048474" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048475" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048476" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048477" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1048478" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{79927C69-A4F3-474B-BE0A-93F745B09823}"/>

--- a/data/ai_data.xlsx
+++ b/data/ai_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\text_mining_project -V2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB2CB6D-9E64-4A1E-98AF-9FC7E07E455E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B21888-DDBA-4F5F-9DFE-4F5048E0A30D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
